--- a/COVID DETERMINANTS IN ARC.xlsx
+++ b/COVID DETERMINANTS IN ARC.xlsx
@@ -1,21 +1,404 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meyssa\OneDrive - University of Ottawa\Desktop\Lemgaamer le B\Covid\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A677037-5ECA-4CBC-AE4A-3BCE8DC62F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+  <si>
+    <t>ONS_ID</t>
+  </si>
+  <si>
+    <t>population_density</t>
+  </si>
+  <si>
+    <t>median_income_after_tax</t>
+  </si>
+  <si>
+    <t>unemployment_rate</t>
+  </si>
+  <si>
+    <t>perc_public_transport_work</t>
+  </si>
+  <si>
+    <t>perc_newcomers</t>
+  </si>
+  <si>
+    <t>avg_household</t>
+  </si>
+  <si>
+    <t>job_density</t>
+  </si>
+  <si>
+    <t>perc_no_hs_diploma</t>
+  </si>
+  <si>
+    <t>perc_bachelors_and_above</t>
+  </si>
+  <si>
+    <t>perc_seniors</t>
+  </si>
+  <si>
+    <t>covid_rate</t>
+  </si>
+  <si>
+    <t>ONS_Name</t>
+  </si>
+  <si>
+    <t>population_density_sqrt</t>
+  </si>
+  <si>
+    <t>unemployment_rate_log</t>
+  </si>
+  <si>
+    <t>perc_newcomers_sqrt</t>
+  </si>
+  <si>
+    <t>avg_household_sq</t>
+  </si>
+  <si>
+    <t>job_density_log</t>
+  </si>
+  <si>
+    <t>perc_no_hs_diploma_sqrt</t>
+  </si>
+  <si>
+    <t>perc_bachelors_and_above_sqrt</t>
+  </si>
+  <si>
+    <t>perc_seniors_log</t>
+  </si>
+  <si>
+    <t>covid_rate_log</t>
+  </si>
+  <si>
+    <t>Beacon Hill South - Cardinal Heights</t>
+  </si>
+  <si>
+    <t>Bells Corners East</t>
+  </si>
+  <si>
+    <t>Bells Corners West</t>
+  </si>
+  <si>
+    <t>Braemar Park - Bel Air Heights - Copeland Park</t>
+  </si>
+  <si>
+    <t>Briar Green - Leslie Park</t>
+  </si>
+  <si>
+    <t>Bridlewood - Emerald Meadows</t>
+  </si>
+  <si>
+    <t>Carleton Heights - Rideauview</t>
+  </si>
+  <si>
+    <t>Carlington</t>
+  </si>
+  <si>
+    <t>Centrepointe</t>
+  </si>
+  <si>
+    <t>Centretown</t>
+  </si>
+  <si>
+    <t>Civic Hospital-Central Park</t>
+  </si>
+  <si>
+    <t>Constance Bay</t>
+  </si>
+  <si>
+    <t>Corkery</t>
+  </si>
+  <si>
+    <t>Cityview - Crestview - Meadowlands</t>
+  </si>
+  <si>
+    <t>Crystal Bay - Lakeview Park</t>
+  </si>
+  <si>
+    <t>Dunrobin</t>
+  </si>
+  <si>
+    <t>Emerald Woods - Sawmill Creek</t>
+  </si>
+  <si>
+    <t>Greenboro East</t>
+  </si>
+  <si>
+    <t>Hawthorne Meadows - Sheffield Glen</t>
+  </si>
+  <si>
+    <t>Hintonburg - Mechanicsville</t>
+  </si>
+  <si>
+    <t>Hunt Club - Ottawa Airport</t>
+  </si>
+  <si>
+    <t>Hunt Club East - Western Community</t>
+  </si>
+  <si>
+    <t>Hunt Club Park</t>
+  </si>
+  <si>
+    <t>Hunt Club Upper -Blossom Park - Timbermill</t>
+  </si>
+  <si>
+    <t>Iris - Queensway Terrance South</t>
+  </si>
+  <si>
+    <t>Island Park - Wellington Village</t>
+  </si>
+  <si>
+    <t>Manotick</t>
+  </si>
+  <si>
+    <t>Merivale Gardens - Grenfell Glen - Pineglen - Country Place</t>
+  </si>
+  <si>
+    <t>Metcalfe</t>
+  </si>
+  <si>
+    <t>Munster - Ashton</t>
+  </si>
+  <si>
+    <t>North Gower - Kars</t>
+  </si>
+  <si>
+    <t>Chapel Hill South</t>
+  </si>
+  <si>
+    <t>Chatelaine Village</t>
+  </si>
+  <si>
+    <t>Osgoode - Vernon</t>
+  </si>
+  <si>
+    <t>Old Ottawa East</t>
+  </si>
+  <si>
+    <t>Old Ottawa South</t>
+  </si>
+  <si>
+    <t>Marlborough</t>
+  </si>
+  <si>
+    <t>Pineview</t>
+  </si>
+  <si>
+    <t>Playfair Park - Lynda Park - Guildwood Estates</t>
+  </si>
+  <si>
+    <t>Qualicum - Redwood Park</t>
+  </si>
+  <si>
+    <t>Riverside Park</t>
+  </si>
+  <si>
+    <t>Rothwell Heights - Beacon Hill North</t>
+  </si>
+  <si>
+    <t>South Keys - Greenboro West</t>
+  </si>
+  <si>
+    <t>Tanglewood</t>
+  </si>
+  <si>
+    <t>Trend-Arlington</t>
+  </si>
+  <si>
+    <t>Whitehaven - Queensway Terrace North</t>
+  </si>
+  <si>
+    <t>Woodvale - Craig Henry - Manordale - Estates of Arlington Woods</t>
+  </si>
+  <si>
+    <t>Bayshore - Belltown</t>
+  </si>
+  <si>
+    <t>Beaverbrook</t>
+  </si>
+  <si>
+    <t>Billings Bridge - Alta Vista</t>
+  </si>
+  <si>
+    <t>Blackburn Hamlet</t>
+  </si>
+  <si>
+    <t>Borden Farm - Fisher Glen</t>
+  </si>
+  <si>
+    <t>Britannia Village</t>
+  </si>
+  <si>
+    <t>Brookside - Briarbrook - Morgan's Grant</t>
+  </si>
+  <si>
+    <t>Byward Market</t>
+  </si>
+  <si>
+    <t>Cardinal Creek</t>
+  </si>
+  <si>
+    <t>Carlingwood West - Glabar Park - McKellar Heights</t>
+  </si>
+  <si>
+    <t>Carp</t>
+  </si>
+  <si>
+    <t>Carson Grove - Carson Meadows</t>
+  </si>
+  <si>
+    <t>Chapel Hill North</t>
+  </si>
+  <si>
+    <t>Chapman Mills</t>
+  </si>
+  <si>
+    <t>Convent Glen - Orléans Woods</t>
+  </si>
+  <si>
+    <t>Cumberland</t>
+  </si>
+  <si>
+    <t>East Industrial</t>
+  </si>
+  <si>
+    <t>Edwards - Carlsbad Springs</t>
+  </si>
+  <si>
+    <t>Elmvale - Canterbury</t>
+  </si>
+  <si>
+    <t>Fallingbrook</t>
+  </si>
+  <si>
+    <t>Findlay Creek</t>
+  </si>
+  <si>
+    <t>Fitzroy</t>
+  </si>
+  <si>
+    <t>Glebe - Dows Lake</t>
+  </si>
+  <si>
+    <t>Glen Cairn - Kanata South Business Park</t>
+  </si>
+  <si>
+    <t>Greely</t>
+  </si>
+  <si>
+    <t>Hunt Club Woods - Quintarra - Revelstoke</t>
+  </si>
+  <si>
+    <t>Kanata Lakes - Arcadia</t>
+  </si>
+  <si>
+    <t>Katimavik - Hazeldean</t>
+  </si>
+  <si>
+    <t>Laurentian</t>
+  </si>
+  <si>
+    <t>Ledbury - Heron Gate - Ridgemont</t>
+  </si>
+  <si>
+    <t>Lindenlea - New Edinburgh</t>
+  </si>
+  <si>
+    <t>Lowertown</t>
+  </si>
+  <si>
+    <t>Manor Park</t>
+  </si>
+  <si>
+    <t>Navan - Sarsfield</t>
+  </si>
+  <si>
+    <t>Old Barrhaven East</t>
+  </si>
+  <si>
+    <t>Old Barrhaven West</t>
+  </si>
+  <si>
+    <t>Orléans Village - Chateauneuf</t>
+  </si>
+  <si>
+    <t>Overbrook - McArthur</t>
+  </si>
+  <si>
+    <t>Parkwood Hills - Stewart Farm</t>
+  </si>
+  <si>
+    <t>Portobello South</t>
+  </si>
+  <si>
+    <t>Queenswood Heights</t>
+  </si>
+  <si>
+    <t>Richmond</t>
+  </si>
+  <si>
+    <t>Rideau Crest - Davidson Heights</t>
+  </si>
+  <si>
+    <t>Riverside South - Leitrim</t>
+  </si>
+  <si>
+    <t>Riverview</t>
+  </si>
+  <si>
+    <t>Rockcliffe Park</t>
+  </si>
+  <si>
+    <t>Sandy Hill</t>
+  </si>
+  <si>
+    <t>Skyline - Fisher Heights</t>
+  </si>
+  <si>
+    <t>Stittsville</t>
+  </si>
+  <si>
+    <t>Stonebridge - Half Moon Bay - Heart's Desire</t>
+  </si>
+  <si>
+    <t>Vanier North</t>
+  </si>
+  <si>
+    <t>Vanier South</t>
+  </si>
+  <si>
+    <t>Vars</t>
+  </si>
+  <si>
+    <t>West Centretown</t>
+  </si>
+  <si>
+    <t>Westboro</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +446,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +498,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +532,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +567,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,123 +743,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="56.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ONS_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>population_density</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>median_income_after_tax</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>unemployment_rate</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>perc_public_transport_work</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>perc_newcomers</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>avg_household</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>job_density</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>perc_no_hs_diploma</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>perc_bachelors_and_above</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>perc_seniors</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>covid_rate</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ONS_Name</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>population_density_sqrt</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>unemployment_rate_log</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>perc_newcomers_sqrt</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>avg_household_sq</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>job_density_log</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>perc_no_hs_diploma_sqrt</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>perc_bachelors_and_above_sqrt</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>perc_seniors_log</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>covid_rate_log</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3</v>
       </c>
@@ -477,66 +850,64 @@
         <v>60643</v>
       </c>
       <c r="D2">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E2">
-        <v>28.55007474</v>
+        <v>28.550074739999999</v>
       </c>
       <c r="F2">
-        <v>5.513439008</v>
+        <v>5.5134390079999998</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H2">
         <v>1528.195731</v>
       </c>
       <c r="I2">
-        <v>8.646616541</v>
+        <v>8.6466165410000002</v>
       </c>
       <c r="J2">
-        <v>33.08270677</v>
+        <v>33.082706770000001</v>
       </c>
       <c r="K2">
-        <v>18.87052342</v>
+        <v>18.870523420000001</v>
       </c>
       <c r="L2">
         <v>4167</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beacon Hill South - Cardinal Heights</t>
-        </is>
+      <c r="M2" t="s">
+        <v>22</v>
       </c>
       <c r="N2">
-        <v>57.03178200792958</v>
+        <v>57.031782007929579</v>
       </c>
       <c r="O2">
-        <v>0.9395192526186185</v>
+        <v>0.93951925261861846</v>
       </c>
       <c r="P2">
-        <v>2.348071337928216</v>
+        <v>2.3480713379282161</v>
       </c>
       <c r="Q2">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R2">
-        <v>3.184178982151517</v>
+        <v>3.1841789821515172</v>
       </c>
       <c r="S2">
-        <v>2.940512972425049</v>
+        <v>2.9405129724250489</v>
       </c>
       <c r="T2">
-        <v>5.751756842044003</v>
+        <v>5.7517568420440028</v>
       </c>
       <c r="U2">
-        <v>1.275783946548878</v>
+        <v>1.2757839465488781</v>
       </c>
       <c r="V2">
-        <v>3.619823500457278</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>3.6198235004572781</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>6</v>
       </c>
@@ -547,19 +918,19 @@
         <v>71338</v>
       </c>
       <c r="D3">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E3">
         <v>16.70588235</v>
       </c>
       <c r="F3">
-        <v>2.183406114</v>
+        <v>2.1834061139999998</v>
       </c>
       <c r="G3">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H3">
-        <v>1630.999715</v>
+        <v>1630.9997149999999</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -568,27 +939,25 @@
         <v>30.6122449</v>
       </c>
       <c r="K3">
-        <v>21.94323144</v>
+        <v>21.943231440000002</v>
       </c>
       <c r="L3">
         <v>2723</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Bells Corners East</t>
-        </is>
+      <c r="M3" t="s">
+        <v>23</v>
       </c>
       <c r="N3">
-        <v>36.94763437623578</v>
+        <v>36.947634376235783</v>
       </c>
       <c r="O3">
-        <v>0.9395192526186185</v>
+        <v>0.93951925261861846</v>
       </c>
       <c r="P3">
         <v>1.477635311570483</v>
       </c>
       <c r="Q3">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R3">
         <v>3.212453885151902</v>
@@ -597,21 +966,21 @@
         <v>3.16227766016838</v>
       </c>
       <c r="T3">
-        <v>5.532833351909309</v>
+        <v>5.5328333519093089</v>
       </c>
       <c r="U3">
-        <v>1.341300583731896</v>
+        <v>1.3413005837318961</v>
       </c>
       <c r="V3">
-        <v>3.435047641339965</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>3.4350476413399651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>3020.355091</v>
+        <v>3020.3550909999999</v>
       </c>
       <c r="C4">
         <v>63370</v>
@@ -620,22 +989,22 @@
         <v>8.1</v>
       </c>
       <c r="E4">
-        <v>21.03960396</v>
+        <v>21.039603960000001</v>
       </c>
       <c r="F4">
         <v>2.053140097</v>
       </c>
       <c r="G4">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H4">
-        <v>2260.888991</v>
+        <v>2260.8889909999998</v>
       </c>
       <c r="I4">
-        <v>6.288032454</v>
+        <v>6.2880324539999997</v>
       </c>
       <c r="J4">
-        <v>28.80324544</v>
+        <v>28.803245440000001</v>
       </c>
       <c r="K4">
         <v>12.68115942</v>
@@ -643,31 +1012,29 @@
       <c r="L4">
         <v>2956</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Bells Corners West</t>
-        </is>
+      <c r="M4" t="s">
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>54.95775733233663</v>
+        <v>54.957757332336627</v>
       </c>
       <c r="O4">
-        <v>0.9084850188786497</v>
+        <v>0.90848501887864974</v>
       </c>
       <c r="P4">
         <v>1.432878256168332</v>
       </c>
       <c r="Q4">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R4">
         <v>3.35427923913453</v>
       </c>
       <c r="S4">
-        <v>2.507594954134339</v>
+        <v>2.5075949541343392</v>
       </c>
       <c r="T4">
-        <v>5.366865513500408</v>
+        <v>5.3668655135004082</v>
       </c>
       <c r="U4">
         <v>1.103158962275131</v>
@@ -676,12 +1043,12 @@
         <v>3.470704429722788</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>2870.271854</v>
+        <v>2870.2718540000001</v>
       </c>
       <c r="C5">
         <v>68904</v>
@@ -693,19 +1060,19 @@
         <v>20.11922504</v>
       </c>
       <c r="F5">
-        <v>3.6954915</v>
+        <v>3.6954915000000002</v>
       </c>
       <c r="G5">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H5">
-        <v>378.1805753</v>
+        <v>378.18057529999999</v>
       </c>
       <c r="I5">
         <v>5.142083897</v>
       </c>
       <c r="J5">
-        <v>46.95534506</v>
+        <v>46.955345059999999</v>
       </c>
       <c r="K5">
         <v>16.17429838</v>
@@ -713,45 +1080,43 @@
       <c r="L5">
         <v>3271</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Braemar Park - Bel Air Heights - Copeland Park</t>
-        </is>
+      <c r="M5" t="s">
+        <v>25</v>
       </c>
       <c r="N5">
-        <v>53.57491814272795</v>
+        <v>53.574918142727952</v>
       </c>
       <c r="O5">
-        <v>0.8633228601204559</v>
+        <v>0.86332286012045589</v>
       </c>
       <c r="P5">
-        <v>1.922366120175863</v>
+        <v>1.9223661201758631</v>
       </c>
       <c r="Q5">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R5">
-        <v>2.577699218171973</v>
+        <v>2.5776992181719729</v>
       </c>
       <c r="S5">
-        <v>2.267616346959953</v>
+        <v>2.2676163469599531</v>
       </c>
       <c r="T5">
-        <v>6.852397030236937</v>
+        <v>6.8523970302369372</v>
       </c>
       <c r="U5">
         <v>1.20882545062029</v>
       </c>
       <c r="V5">
-        <v>3.514680544124982</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>3.5146805441249822</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>2722.83582</v>
+        <v>2722.8358199999998</v>
       </c>
       <c r="C6">
         <v>72145</v>
@@ -760,68 +1125,66 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>21.70542636</v>
+        <v>21.705426360000001</v>
       </c>
       <c r="F6">
-        <v>3.37512054</v>
+        <v>3.3751205400000002</v>
       </c>
       <c r="G6">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H6">
-        <v>349.0276032</v>
+        <v>349.02760319999999</v>
       </c>
       <c r="I6">
-        <v>3.907637655</v>
+        <v>3.9076376549999998</v>
       </c>
       <c r="J6">
-        <v>49.20071048</v>
+        <v>49.200710479999998</v>
       </c>
       <c r="K6">
-        <v>19.30501931</v>
+        <v>19.305019309999999</v>
       </c>
       <c r="L6">
         <v>3280</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Briar Green - Leslie Park</t>
-        </is>
+      <c r="M6" t="s">
+        <v>26</v>
       </c>
       <c r="N6">
-        <v>52.18079934228681</v>
+        <v>52.180799342286811</v>
       </c>
       <c r="O6">
-        <v>0.8450980400142568</v>
+        <v>0.84509804001425681</v>
       </c>
       <c r="P6">
         <v>1.837150113627082</v>
       </c>
       <c r="Q6">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R6">
-        <v>2.542859774934515</v>
+        <v>2.5428597749345152</v>
       </c>
       <c r="S6">
-        <v>1.976774558466392</v>
+        <v>1.9767745584663921</v>
       </c>
       <c r="T6">
-        <v>7.014321811836123</v>
+        <v>7.0143218118361226</v>
       </c>
       <c r="U6">
         <v>1.285670240366815</v>
       </c>
       <c r="V6">
-        <v>3.515873843711679</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>3.5158738437116792</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>3723.524708</v>
+        <v>3723.5247079999999</v>
       </c>
       <c r="C7">
         <v>96364</v>
@@ -833,7 +1196,7 @@
         <v>15.40650407</v>
       </c>
       <c r="F7">
-        <v>2.351485149</v>
+        <v>2.3514851490000002</v>
       </c>
       <c r="G7">
         <v>2.9</v>
@@ -842,10 +1205,10 @@
         <v>173.272932</v>
       </c>
       <c r="I7">
-        <v>4.055059524</v>
+        <v>4.0550595239999998</v>
       </c>
       <c r="J7">
-        <v>48.69791667</v>
+        <v>48.697916669999998</v>
       </c>
       <c r="K7">
         <v>10.27227723</v>
@@ -853,16 +1216,14 @@
       <c r="L7">
         <v>2703</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Bridlewood - Emerald Meadows</t>
-        </is>
+      <c r="M7" t="s">
+        <v>27</v>
       </c>
       <c r="N7">
-        <v>61.02069081877065</v>
+        <v>61.020690818770653</v>
       </c>
       <c r="O7">
-        <v>0.8129133566428556</v>
+        <v>0.81291335664285558</v>
       </c>
       <c r="P7">
         <v>1.533455297359529</v>
@@ -871,13 +1232,13 @@
         <v>8.41</v>
       </c>
       <c r="R7">
-        <v>2.238730724276609</v>
+        <v>2.2387307242766088</v>
       </c>
       <c r="S7">
-        <v>2.013717836242208</v>
+        <v>2.0137178362422081</v>
       </c>
       <c r="T7">
-        <v>6.978389260423927</v>
+        <v>6.9783892604239268</v>
       </c>
       <c r="U7">
         <v>1.011666731697765</v>
@@ -886,12 +1247,12 @@
         <v>3.431846045698725</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>16</v>
       </c>
       <c r="B8">
-        <v>2992.953922</v>
+        <v>2992.9539220000001</v>
       </c>
       <c r="C8">
         <v>51743</v>
@@ -900,68 +1261,66 @@
         <v>11.6</v>
       </c>
       <c r="E8">
-        <v>21.69491525</v>
+        <v>21.694915250000001</v>
       </c>
       <c r="F8">
-        <v>3.993735317</v>
+        <v>3.9937353170000001</v>
       </c>
       <c r="G8">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H8">
-        <v>606.5594948</v>
+        <v>606.55949480000004</v>
       </c>
       <c r="I8">
-        <v>7.836990596</v>
+        <v>7.8369905959999997</v>
       </c>
       <c r="J8">
-        <v>49.52978056</v>
+        <v>49.529780559999999</v>
       </c>
       <c r="K8">
-        <v>15.74001566</v>
+        <v>15.740015659999999</v>
       </c>
       <c r="L8">
         <v>4151</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Carleton Heights - Rideauview</t>
-        </is>
+      <c r="M8" t="s">
+        <v>28</v>
       </c>
       <c r="N8">
         <v>54.70789634047356</v>
       </c>
       <c r="O8">
-        <v>1.064457989226918</v>
+        <v>1.0644579892269179</v>
       </c>
       <c r="P8">
-        <v>1.998433215546619</v>
+        <v>1.9984332155466189</v>
       </c>
       <c r="Q8">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R8">
-        <v>2.782873405361073</v>
+        <v>2.7828734053610731</v>
       </c>
       <c r="S8">
-        <v>2.799462554848698</v>
+        <v>2.7994625548486982</v>
       </c>
       <c r="T8">
         <v>7.03773973374975</v>
       </c>
       <c r="U8">
-        <v>1.197005160109971</v>
+        <v>1.1970051601099709</v>
       </c>
       <c r="V8">
-        <v>3.61815273337852</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>3.6181527333785199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>3618.869826</v>
+        <v>3618.8698260000001</v>
       </c>
       <c r="C9">
         <v>43986</v>
@@ -970,124 +1329,120 @@
         <v>10.8</v>
       </c>
       <c r="E9">
-        <v>27.96208531</v>
+        <v>27.962085309999999</v>
       </c>
       <c r="F9">
-        <v>3.413143148</v>
+        <v>3.4131431480000001</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H9">
         <v>2420.073132</v>
       </c>
       <c r="I9">
-        <v>15.14336918</v>
+        <v>15.143369180000001</v>
       </c>
       <c r="J9">
         <v>30.28673835</v>
       </c>
       <c r="K9">
-        <v>10.69246436</v>
+        <v>10.692464360000001</v>
       </c>
       <c r="L9">
         <v>4239</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Carlington</t>
-        </is>
+      <c r="M9" t="s">
+        <v>29</v>
       </c>
       <c r="N9">
-        <v>60.15704302905853</v>
+        <v>60.157043029058528</v>
       </c>
       <c r="O9">
-        <v>1.03342375548695</v>
+        <v>1.0334237554869501</v>
       </c>
       <c r="P9">
-        <v>1.847469390274166</v>
+        <v>1.8474693902741659</v>
       </c>
       <c r="Q9">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R9">
         <v>3.383828490089587</v>
       </c>
       <c r="S9">
-        <v>3.891448211141965</v>
+        <v>3.8914482111419648</v>
       </c>
       <c r="T9">
         <v>5.503338836560947</v>
       </c>
       <c r="U9">
-        <v>1.029077811345858</v>
+        <v>1.0290778113458581</v>
       </c>
       <c r="V9">
-        <v>3.627263416568221</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>3.6272634165682209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>23</v>
       </c>
       <c r="B10">
-        <v>3292.532496</v>
+        <v>3292.5324959999998</v>
       </c>
       <c r="C10">
         <v>91960</v>
       </c>
       <c r="D10">
-        <v>8.199999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E10">
         <v>24.31610942</v>
       </c>
       <c r="F10">
-        <v>3.87374462</v>
+        <v>3.8737446200000001</v>
       </c>
       <c r="G10">
         <v>2.6</v>
       </c>
       <c r="H10">
-        <v>2362.876262</v>
+        <v>2362.8762620000002</v>
       </c>
       <c r="I10">
-        <v>2.890932983</v>
+        <v>2.8909329829999999</v>
       </c>
       <c r="J10">
         <v>66.36005256</v>
       </c>
       <c r="K10">
-        <v>14.13199426</v>
+        <v>14.131994260000001</v>
       </c>
       <c r="L10">
         <v>2479</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Centrepointe</t>
-        </is>
+      <c r="M10" t="s">
+        <v>30</v>
       </c>
       <c r="N10">
-        <v>57.38059337441536</v>
+        <v>57.380593374415362</v>
       </c>
       <c r="O10">
-        <v>0.9138138523837167</v>
+        <v>0.91381385238371671</v>
       </c>
       <c r="P10">
-        <v>1.968183075834156</v>
+        <v>1.9681830758341561</v>
       </c>
       <c r="Q10">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R10">
-        <v>3.373440979297346</v>
+        <v>3.3734409792973459</v>
       </c>
       <c r="S10">
-        <v>1.700274384621494</v>
+        <v>1.7002743846214941</v>
       </c>
       <c r="T10">
-        <v>8.146167967823889</v>
+        <v>8.1461679678238887</v>
       </c>
       <c r="U10">
         <v>1.150203452365212</v>
@@ -1096,12 +1451,12 @@
         <v>3.394276526767821</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>24</v>
       </c>
       <c r="B11">
-        <v>8354.541019</v>
+        <v>8354.5410190000002</v>
       </c>
       <c r="C11">
         <v>51272</v>
@@ -1110,22 +1465,22 @@
         <v>6.8</v>
       </c>
       <c r="E11">
-        <v>21.36678201</v>
+        <v>21.366782010000001</v>
       </c>
       <c r="F11">
-        <v>3.002144389</v>
+        <v>3.0021443890000001</v>
       </c>
       <c r="G11">
         <v>1.5</v>
       </c>
       <c r="H11">
-        <v>31300.64542</v>
+        <v>31300.645420000001</v>
       </c>
       <c r="I11">
-        <v>3.739288496</v>
+        <v>3.7392884959999999</v>
       </c>
       <c r="J11">
-        <v>62.42534407</v>
+        <v>62.425344070000001</v>
       </c>
       <c r="K11">
         <v>12.18509916</v>
@@ -1133,45 +1488,43 @@
       <c r="L11">
         <v>3917</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Centretown</t>
-        </is>
+      <c r="M11" t="s">
+        <v>31</v>
       </c>
       <c r="N11">
-        <v>91.40317838565572</v>
+        <v>91.403178385655721</v>
       </c>
       <c r="O11">
-        <v>0.8325089127062363</v>
+        <v>0.83250891270623628</v>
       </c>
       <c r="P11">
-        <v>1.732669728771182</v>
+        <v>1.7326697287711821</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
       </c>
       <c r="R11">
-        <v>4.495553292800588</v>
+        <v>4.4955532928005884</v>
       </c>
       <c r="S11">
-        <v>1.933723996851671</v>
+        <v>1.9337239968516711</v>
       </c>
       <c r="T11">
-        <v>7.900971083987081</v>
+        <v>7.9009710839870806</v>
       </c>
       <c r="U11">
-        <v>1.085829067740324</v>
+        <v>1.0858290677403239</v>
       </c>
       <c r="V11">
         <v>3.592953571547866</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>28</v>
       </c>
       <c r="B12">
-        <v>1454.314084</v>
+        <v>1454.3140840000001</v>
       </c>
       <c r="C12">
         <v>75258</v>
@@ -1180,19 +1533,19 @@
         <v>5.8</v>
       </c>
       <c r="E12">
-        <v>19.89247312</v>
+        <v>19.892473119999998</v>
       </c>
       <c r="F12">
-        <v>2.883295195</v>
+        <v>2.8832951950000001</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H12">
         <v>2125.669148</v>
       </c>
       <c r="I12">
-        <v>5.868167203</v>
+        <v>5.8681672029999996</v>
       </c>
       <c r="J12">
         <v>57.39549839</v>
@@ -1203,45 +1556,43 @@
       <c r="L12">
         <v>3416</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Civic Hospital-Central Park</t>
-        </is>
+      <c r="M12" t="s">
+        <v>32</v>
       </c>
       <c r="N12">
-        <v>38.13547015574871</v>
+        <v>38.135470155748713</v>
       </c>
       <c r="O12">
-        <v>0.7634279935629372</v>
+        <v>0.76342799356293722</v>
       </c>
       <c r="P12">
-        <v>1.698026853439014</v>
+        <v>1.6980268534390139</v>
       </c>
       <c r="Q12">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R12">
         <v>3.327495669227956</v>
       </c>
       <c r="S12">
-        <v>2.422430020248263</v>
+        <v>2.4224300202482629</v>
       </c>
       <c r="T12">
-        <v>7.575981678304139</v>
+        <v>7.5759816783041387</v>
       </c>
       <c r="U12">
         <v>1.226595184645539</v>
       </c>
       <c r="V12">
-        <v>3.533517862016967</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3.5335178620169669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>29</v>
       </c>
       <c r="B13">
-        <v>377.1694155</v>
+        <v>377.16941550000001</v>
       </c>
       <c r="C13">
         <v>73140</v>
@@ -1250,7 +1601,7 @@
         <v>8.5</v>
       </c>
       <c r="E13">
-        <v>3.03030303</v>
+        <v>3.0303030299999998</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1259,10 +1610,10 @@
         <v>2.4</v>
       </c>
       <c r="H13">
-        <v>12.7135758</v>
+        <v>12.713575799999999</v>
       </c>
       <c r="I13">
-        <v>7.299270073</v>
+        <v>7.2992700729999997</v>
       </c>
       <c r="J13">
         <v>19.34306569</v>
@@ -1273,16 +1624,14 @@
       <c r="L13">
         <v>1811</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Constance Bay</t>
-        </is>
+      <c r="M13" t="s">
+        <v>33</v>
       </c>
       <c r="N13">
-        <v>19.42085002001715</v>
+        <v>19.420850020017149</v>
       </c>
       <c r="O13">
-        <v>0.9294189257142927</v>
+        <v>0.92941892571429274</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1291,22 +1640,22 @@
         <v>5.76</v>
       </c>
       <c r="R13">
-        <v>1.104267716706468</v>
+        <v>1.1042677167064681</v>
       </c>
       <c r="S13">
-        <v>2.701716134792847</v>
+        <v>2.7017161347928469</v>
       </c>
       <c r="T13">
-        <v>4.398075225595852</v>
+        <v>4.3980752255958517</v>
       </c>
       <c r="U13">
-        <v>1.129791239485952</v>
+        <v>1.1297912394859519</v>
       </c>
       <c r="V13">
         <v>3.257918450314059</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>30</v>
       </c>
@@ -1320,22 +1669,22 @@
         <v>5</v>
       </c>
       <c r="E14">
-        <v>4.33604336</v>
+        <v>4.3360433599999997</v>
       </c>
       <c r="F14">
-        <v>1.086956522</v>
+        <v>1.0869565219999999</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>3.244631851</v>
+        <v>3.2446318509999998</v>
       </c>
       <c r="I14">
-        <v>2.716049383</v>
+        <v>2.7160493830000001</v>
       </c>
       <c r="J14">
-        <v>35.30864198</v>
+        <v>35.308641979999997</v>
       </c>
       <c r="K14">
         <v>12.77173913</v>
@@ -1343,19 +1692,17 @@
       <c r="L14">
         <v>1942</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Corkery</t>
-        </is>
+      <c r="M14" t="s">
+        <v>34</v>
       </c>
       <c r="N14">
-        <v>5.139695682625577</v>
+        <v>5.1396956826255771</v>
       </c>
       <c r="O14">
-        <v>0.6989700043360189</v>
+        <v>0.69897000433601886</v>
       </c>
       <c r="P14">
-        <v>1.042572070410482</v>
+        <v>1.0425720704104819</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1367,21 +1714,21 @@
         <v>1.648044108329628</v>
       </c>
       <c r="T14">
-        <v>5.94210753689295</v>
+        <v>5.9421075368929497</v>
       </c>
       <c r="U14">
-        <v>1.106250039247415</v>
+        <v>1.1062500392474151</v>
       </c>
       <c r="V14">
         <v>3.288249225571986</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>31</v>
       </c>
       <c r="B15">
-        <v>2187.707262</v>
+        <v>2187.7072619999999</v>
       </c>
       <c r="C15">
         <v>69305</v>
@@ -1390,10 +1737,10 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>22.37001209</v>
+        <v>22.370012089999999</v>
       </c>
       <c r="F15">
-        <v>3.817235396</v>
+        <v>3.8172353960000001</v>
       </c>
       <c r="G15">
         <v>2.5</v>
@@ -1402,10 +1749,10 @@
         <v>1909.340809</v>
       </c>
       <c r="I15">
-        <v>7.210401891</v>
+        <v>7.2104018910000001</v>
       </c>
       <c r="J15">
-        <v>37.70685579</v>
+        <v>37.706855789999999</v>
       </c>
       <c r="K15">
         <v>18.79699248</v>
@@ -1413,10 +1760,8 @@
       <c r="L15">
         <v>5004</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Cityview - Crestview - Meadowlands</t>
-        </is>
+      <c r="M15" t="s">
+        <v>35</v>
       </c>
       <c r="N15">
         <v>46.77293300617356</v>
@@ -1437,21 +1782,21 @@
         <v>2.685219151391558</v>
       </c>
       <c r="T15">
-        <v>6.140590833950752</v>
+        <v>6.1405908339507516</v>
       </c>
       <c r="U15">
-        <v>1.274088367677157</v>
+        <v>1.2740883676771571</v>
       </c>
       <c r="V15">
-        <v>3.699317301021382</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>3.6993173010213818</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>32</v>
       </c>
       <c r="B16">
-        <v>695.2907999</v>
+        <v>695.29079990000002</v>
       </c>
       <c r="C16">
         <v>87835</v>
@@ -1463,13 +1808,13 @@
         <v>12.1875</v>
       </c>
       <c r="F16">
-        <v>2.219321149</v>
+        <v>2.2193211490000002</v>
       </c>
       <c r="G16">
         <v>2.4</v>
       </c>
       <c r="H16">
-        <v>254.9097431</v>
+        <v>254.90974309999999</v>
       </c>
       <c r="I16">
         <v>5.050505051</v>
@@ -1478,24 +1823,22 @@
         <v>59.5959596</v>
       </c>
       <c r="K16">
-        <v>24.25032595</v>
+        <v>24.250325950000001</v>
       </c>
       <c r="L16">
         <v>2189</v>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Crystal Bay - Lakeview Park</t>
-        </is>
+      <c r="M16" t="s">
+        <v>36</v>
       </c>
       <c r="N16">
-        <v>26.36836741059257</v>
+        <v>26.368367410592569</v>
       </c>
       <c r="O16">
-        <v>0.9030899869919435</v>
+        <v>0.90308998699194354</v>
       </c>
       <c r="P16">
-        <v>1.489738617677611</v>
+        <v>1.4897386176776111</v>
       </c>
       <c r="Q16">
         <v>5.76</v>
@@ -1504,24 +1847,24 @@
         <v>2.406386435287629</v>
       </c>
       <c r="S16">
-        <v>2.247332874987593</v>
+        <v>2.2473328749875932</v>
       </c>
       <c r="T16">
-        <v>7.719841941387142</v>
+        <v>7.7198419413871422</v>
       </c>
       <c r="U16">
         <v>1.38471758035416</v>
       </c>
       <c r="V16">
-        <v>3.340245761567932</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>3.3402457615679322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>35</v>
       </c>
       <c r="B17">
-        <v>46.51475159</v>
+        <v>46.514751590000003</v>
       </c>
       <c r="C17">
         <v>105521</v>
@@ -1530,22 +1873,22 @@
         <v>5.8</v>
       </c>
       <c r="E17">
-        <v>5.37428023</v>
+        <v>5.3742802300000001</v>
       </c>
       <c r="F17">
-        <v>0.593220339</v>
+        <v>0.59322033900000004</v>
       </c>
       <c r="G17">
         <v>2.9</v>
       </c>
       <c r="H17">
-        <v>6.835303328</v>
+        <v>6.8353033280000002</v>
       </c>
       <c r="I17">
-        <v>2.922077922</v>
+        <v>2.9220779220000002</v>
       </c>
       <c r="J17">
-        <v>40.25974026</v>
+        <v>40.259740260000001</v>
       </c>
       <c r="K17">
         <v>15.59322034</v>
@@ -1553,45 +1896,43 @@
       <c r="L17">
         <v>1930</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Dunrobin</t>
-        </is>
+      <c r="M17" t="s">
+        <v>37</v>
       </c>
       <c r="N17">
-        <v>6.820172401779885</v>
+        <v>6.8201724017798853</v>
       </c>
       <c r="O17">
-        <v>0.7634279935629372</v>
+        <v>0.76342799356293722</v>
       </c>
       <c r="P17">
-        <v>0.7702079842484106</v>
+        <v>0.77020798424841064</v>
       </c>
       <c r="Q17">
         <v>8.41</v>
       </c>
       <c r="R17">
-        <v>0.8347577918743769</v>
+        <v>0.83475779187437693</v>
       </c>
       <c r="S17">
-        <v>1.709408646871777</v>
+        <v>1.7094086468717771</v>
       </c>
       <c r="T17">
         <v>6.345056363815849</v>
       </c>
       <c r="U17">
-        <v>1.192935815731735</v>
+        <v>1.1929358157317349</v>
       </c>
       <c r="V17">
-        <v>3.285557309007774</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>3.2855573090077739</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>38</v>
       </c>
       <c r="B18">
-        <v>3095.261248</v>
+        <v>3095.2612479999998</v>
       </c>
       <c r="C18">
         <v>52578</v>
@@ -1600,10 +1941,10 @@
         <v>13.8</v>
       </c>
       <c r="E18">
-        <v>26.80652681</v>
+        <v>26.806526810000001</v>
       </c>
       <c r="F18">
-        <v>11.40819964</v>
+        <v>11.408199639999999</v>
       </c>
       <c r="G18">
         <v>2.6</v>
@@ -1615,7 +1956,7 @@
         <v>13.11754685</v>
       </c>
       <c r="J18">
-        <v>31.51618399</v>
+        <v>31.516183989999998</v>
       </c>
       <c r="K18">
         <v>13.36898396</v>
@@ -1623,22 +1964,20 @@
       <c r="L18">
         <v>7486</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Emerald Woods - Sawmill Creek</t>
-        </is>
+      <c r="M18" t="s">
+        <v>38</v>
       </c>
       <c r="N18">
-        <v>55.63507210384471</v>
+        <v>55.635072103844713</v>
       </c>
       <c r="O18">
         <v>1.139879086401236</v>
       </c>
       <c r="P18">
-        <v>3.377602646848797</v>
+        <v>3.3776026468487972</v>
       </c>
       <c r="Q18">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R18">
         <v>2.604461977590784</v>
@@ -1647,7 +1986,7 @@
         <v>3.621815408051603</v>
       </c>
       <c r="T18">
-        <v>5.613927679441551</v>
+        <v>5.6139276794415514</v>
       </c>
       <c r="U18">
         <v>1.126098402225872</v>
@@ -1656,12 +1995,12 @@
         <v>3.874249822778403</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>45</v>
       </c>
       <c r="B19">
-        <v>4899.918313</v>
+        <v>4899.9183130000001</v>
       </c>
       <c r="C19">
         <v>70699</v>
@@ -1673,7 +2012,7 @@
         <v>23.6453202</v>
       </c>
       <c r="F19">
-        <v>4.178403756</v>
+        <v>4.1784037559999998</v>
       </c>
       <c r="G19">
         <v>2.8</v>
@@ -1682,56 +2021,54 @@
         <v>228.6628546</v>
       </c>
       <c r="I19">
-        <v>7.064760303</v>
+        <v>7.0647603029999999</v>
       </c>
       <c r="J19">
         <v>42.89318755</v>
       </c>
       <c r="K19">
-        <v>8.826291080000001</v>
+        <v>8.8262910800000007</v>
       </c>
       <c r="L19">
         <v>5113</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Greenboro East</t>
-        </is>
+      <c r="M19" t="s">
+        <v>39</v>
       </c>
       <c r="N19">
-        <v>69.99941651899678</v>
+        <v>69.999416518996782</v>
       </c>
       <c r="O19">
-        <v>0.9777236052888477</v>
+        <v>0.97772360528884772</v>
       </c>
       <c r="P19">
-        <v>2.044114418519668</v>
+        <v>2.0441144185196678</v>
       </c>
       <c r="Q19">
         <v>7.839999999999999</v>
       </c>
       <c r="R19">
-        <v>2.359195620870539</v>
+        <v>2.3591956208705391</v>
       </c>
       <c r="S19">
         <v>2.657961682003712</v>
       </c>
       <c r="T19">
-        <v>6.549289087374293</v>
+        <v>6.5492890873742926</v>
       </c>
       <c r="U19">
-        <v>0.9457782458341825</v>
+        <v>0.94577824583418246</v>
       </c>
       <c r="V19">
-        <v>3.708675792726537</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>3.7086757927265368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>46</v>
       </c>
       <c r="B20">
-        <v>5736.118518</v>
+        <v>5736.1185180000002</v>
       </c>
       <c r="C20">
         <v>45765</v>
@@ -1740,36 +2077,34 @@
         <v>11.8</v>
       </c>
       <c r="E20">
-        <v>32.14920071</v>
+        <v>32.149200710000002</v>
       </c>
       <c r="F20">
-        <v>7.524454477</v>
+        <v>7.5244544769999999</v>
       </c>
       <c r="G20">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H20">
-        <v>811.1770011</v>
+        <v>811.17700109999998</v>
       </c>
       <c r="I20">
         <v>15.25885559</v>
       </c>
       <c r="J20">
-        <v>26.97547684</v>
+        <v>26.975476839999999</v>
       </c>
       <c r="K20">
-        <v>14.0060241</v>
+        <v>14.006024099999999</v>
       </c>
       <c r="L20">
         <v>5699</v>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Hawthorne Meadows - Sheffield Glen</t>
-        </is>
+      <c r="M20" t="s">
+        <v>40</v>
       </c>
       <c r="N20">
-        <v>75.73716734866706</v>
+        <v>75.737167348667057</v>
       </c>
       <c r="O20">
         <v>1.071882007306125</v>
@@ -1778,30 +2113,30 @@
         <v>2.743073910232825</v>
       </c>
       <c r="Q20">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R20">
-        <v>2.909115628827334</v>
+        <v>2.9091156288273341</v>
       </c>
       <c r="S20">
-        <v>3.906258515510718</v>
+        <v>3.9062585155107179</v>
       </c>
       <c r="T20">
         <v>5.193792144474016</v>
       </c>
       <c r="U20">
-        <v>1.146314869297994</v>
+        <v>1.1463148692979941</v>
       </c>
       <c r="V20">
         <v>3.75579865697383</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>47</v>
       </c>
       <c r="B21">
-        <v>5335.994641</v>
+        <v>5335.9946410000002</v>
       </c>
       <c r="C21">
         <v>52100</v>
@@ -1819,13 +2154,13 @@
         <v>1.8</v>
       </c>
       <c r="H21">
-        <v>3049.919227</v>
+        <v>3049.9192269999999</v>
       </c>
       <c r="I21">
-        <v>5.210727969</v>
+        <v>5.2107279689999997</v>
       </c>
       <c r="J21">
-        <v>55.24904215</v>
+        <v>55.249042150000001</v>
       </c>
       <c r="K21">
         <v>12.73006135</v>
@@ -1833,16 +2168,14 @@
       <c r="L21">
         <v>3249</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Hintonburg - Mechanicsville</t>
-        </is>
+      <c r="M21" t="s">
+        <v>41</v>
       </c>
       <c r="N21">
-        <v>73.04789278959387</v>
+        <v>73.047892789593874</v>
       </c>
       <c r="O21">
-        <v>0.7993405494535817</v>
+        <v>0.79934054945358168</v>
       </c>
       <c r="P21">
         <v>1.393822185933342</v>
@@ -1857,16 +2190,16 @@
         <v>2.282701901037453</v>
       </c>
       <c r="T21">
-        <v>7.432969941416419</v>
+        <v>7.4329699414164194</v>
       </c>
       <c r="U21">
         <v>1.104830496654619</v>
       </c>
       <c r="V21">
-        <v>3.511749711344983</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>3.5117497113449829</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>48</v>
       </c>
@@ -1880,7 +2213,7 @@
         <v>6.6</v>
       </c>
       <c r="E22">
-        <v>19.13875598</v>
+        <v>19.138755979999999</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1889,13 +2222,13 @@
         <v>2.6</v>
       </c>
       <c r="H22">
-        <v>564.1108085</v>
+        <v>564.11080849999996</v>
       </c>
       <c r="I22">
-        <v>4.435483871</v>
+        <v>4.4354838709999997</v>
       </c>
       <c r="J22">
-        <v>39.51612903</v>
+        <v>39.516129030000002</v>
       </c>
       <c r="K22">
         <v>7.692307692</v>
@@ -1903,40 +2236,38 @@
       <c r="L22">
         <v>4324</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Hunt Club - Ottawa Airport</t>
-        </is>
+      <c r="M22" t="s">
+        <v>42</v>
       </c>
       <c r="N22">
-        <v>11.47529925099995</v>
+        <v>11.475299250999949</v>
       </c>
       <c r="O22">
-        <v>0.8195439355418687</v>
+        <v>0.81954393554186866</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R22">
-        <v>2.751364420992789</v>
+        <v>2.7513644209927892</v>
       </c>
       <c r="S22">
-        <v>2.106058847943238</v>
+        <v>2.1060588479432378</v>
       </c>
       <c r="T22">
-        <v>6.286185570757516</v>
+        <v>6.2861855707575156</v>
       </c>
       <c r="U22">
         <v>0.8860566476757914</v>
       </c>
       <c r="V22">
-        <v>3.635885685281273</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>3.6358856852812731</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>49</v>
       </c>
@@ -1947,80 +2278,78 @@
         <v>64047</v>
       </c>
       <c r="D23">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E23">
-        <v>27.36373749</v>
+        <v>27.363737489999998</v>
       </c>
       <c r="F23">
-        <v>6.568300809</v>
+        <v>6.5683008090000001</v>
       </c>
       <c r="G23">
         <v>2.6</v>
       </c>
       <c r="H23">
-        <v>226.5722492</v>
+        <v>226.57224919999999</v>
       </c>
       <c r="I23">
-        <v>9.659613615</v>
+        <v>9.6596136149999996</v>
       </c>
       <c r="J23">
-        <v>38.54645814</v>
+        <v>38.546458139999999</v>
       </c>
       <c r="K23">
-        <v>15.80199905</v>
+        <v>15.801999049999999</v>
       </c>
       <c r="L23">
         <v>5000</v>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Hunt Club East - Western Community</t>
-        </is>
+      <c r="M23" t="s">
+        <v>43</v>
       </c>
       <c r="N23">
-        <v>55.38224107058146</v>
+        <v>55.382241070581458</v>
       </c>
       <c r="O23">
         <v>1.008600171761918</v>
       </c>
       <c r="P23">
-        <v>2.562869643388052</v>
+        <v>2.5628696433880518</v>
       </c>
       <c r="Q23">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R23">
         <v>2.355206715953901</v>
       </c>
       <c r="S23">
-        <v>3.107991894294449</v>
+        <v>3.1079918942944489</v>
       </c>
       <c r="T23">
-        <v>6.208579397897719</v>
+        <v>6.2085793978977186</v>
       </c>
       <c r="U23">
         <v>1.198712031351062</v>
       </c>
       <c r="V23">
-        <v>3.698970004336019</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>3.6989700043360192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>50</v>
       </c>
       <c r="B24">
-        <v>4844.926012</v>
+        <v>4844.9260119999999</v>
       </c>
       <c r="C24">
         <v>76221</v>
       </c>
       <c r="D24">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E24">
-        <v>19.44792974</v>
+        <v>19.447929739999999</v>
       </c>
       <c r="F24">
         <v>3.741496599</v>
@@ -2029,13 +2358,13 @@
         <v>3</v>
       </c>
       <c r="H24">
-        <v>254.33115</v>
+        <v>254.33115000000001</v>
       </c>
       <c r="I24">
-        <v>9.830866808</v>
+        <v>9.8308668079999997</v>
       </c>
       <c r="J24">
-        <v>39.42917548</v>
+        <v>39.429175479999998</v>
       </c>
       <c r="K24">
         <v>10.65759637</v>
@@ -2043,31 +2372,29 @@
       <c r="L24">
         <v>5812</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Hunt Club Park</t>
-        </is>
+      <c r="M24" t="s">
+        <v>44</v>
       </c>
       <c r="N24">
-        <v>69.60550274224015</v>
+        <v>69.605502742240148</v>
       </c>
       <c r="O24">
-        <v>0.9395192526186185</v>
+        <v>0.93951925261861846</v>
       </c>
       <c r="P24">
-        <v>1.934294858339855</v>
+        <v>1.9342948583398549</v>
       </c>
       <c r="Q24">
         <v>9</v>
       </c>
       <c r="R24">
-        <v>2.405399555003152</v>
+        <v>2.4053995550031519</v>
       </c>
       <c r="S24">
-        <v>3.135421312678728</v>
+        <v>3.1354213126787278</v>
       </c>
       <c r="T24">
-        <v>6.279265520743648</v>
+        <v>6.2792655207436479</v>
       </c>
       <c r="U24">
         <v>1.027659268391184</v>
@@ -2076,7 +2403,7 @@
         <v>3.764325605625984</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>52</v>
       </c>
@@ -2090,22 +2417,22 @@
         <v>8.1</v>
       </c>
       <c r="E25">
-        <v>18.11320755</v>
+        <v>18.113207549999998</v>
       </c>
       <c r="F25">
-        <v>3.64614465</v>
+        <v>3.6461446500000001</v>
       </c>
       <c r="G25">
         <v>2.9</v>
       </c>
       <c r="H25">
-        <v>364.2610934</v>
+        <v>364.26109339999999</v>
       </c>
       <c r="I25">
-        <v>9.07079646</v>
+        <v>9.0707964600000004</v>
       </c>
       <c r="J25">
-        <v>37.16814159</v>
+        <v>37.168141589999998</v>
       </c>
       <c r="K25">
         <v>12.25343694</v>
@@ -2113,45 +2440,43 @@
       <c r="L25">
         <v>4528</v>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Hunt Club Upper -Blossom Park - Timbermill</t>
-        </is>
+      <c r="M25" t="s">
+        <v>45</v>
       </c>
       <c r="N25">
-        <v>43.79024927994816</v>
+        <v>43.790249279948164</v>
       </c>
       <c r="O25">
-        <v>0.9084850188786497</v>
+        <v>0.90848501887864974</v>
       </c>
       <c r="P25">
-        <v>1.90948805966416</v>
+        <v>1.9094880596641599</v>
       </c>
       <c r="Q25">
         <v>8.41</v>
       </c>
       <c r="R25">
-        <v>2.561412786877286</v>
+        <v>2.5614127868772858</v>
       </c>
       <c r="S25">
         <v>3.011776296473561</v>
       </c>
       <c r="T25">
-        <v>6.096568017335655</v>
+        <v>6.0965680173356551</v>
       </c>
       <c r="U25">
         <v>1.088257920106495</v>
       </c>
       <c r="V25">
-        <v>3.655906418180215</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>3.6559064181802148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>54</v>
       </c>
       <c r="B26">
-        <v>2730.608442</v>
+        <v>2730.6084420000002</v>
       </c>
       <c r="C26">
         <v>58230</v>
@@ -2160,22 +2485,22 @@
         <v>8</v>
       </c>
       <c r="E26">
-        <v>30.42016807</v>
+        <v>30.420168069999999</v>
       </c>
       <c r="F26">
-        <v>4.757858963</v>
+        <v>4.7578589630000003</v>
       </c>
       <c r="G26">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H26">
-        <v>1218.913913</v>
+        <v>1218.9139130000001</v>
       </c>
       <c r="I26">
-        <v>7.774390244</v>
+        <v>7.7743902440000001</v>
       </c>
       <c r="J26">
-        <v>30.79268293</v>
+        <v>30.792682930000002</v>
       </c>
       <c r="K26">
         <v>14.18861512</v>
@@ -2183,45 +2508,43 @@
       <c r="L26">
         <v>3718</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Iris - Queensway Terrance South</t>
-        </is>
+      <c r="M26" t="s">
+        <v>46</v>
       </c>
       <c r="N26">
-        <v>52.25522406420242</v>
+        <v>52.255224064202423</v>
       </c>
       <c r="O26">
-        <v>0.9030899869919435</v>
+        <v>0.90308998699194354</v>
       </c>
       <c r="P26">
-        <v>2.181251696389025</v>
+        <v>2.1812516963890252</v>
       </c>
       <c r="Q26">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R26">
-        <v>3.085973034224384</v>
+        <v>3.0859730342243838</v>
       </c>
       <c r="S26">
-        <v>2.788259357376928</v>
+        <v>2.7882593573769281</v>
       </c>
       <c r="T26">
         <v>5.549115508799578</v>
       </c>
       <c r="U26">
-        <v>1.151940008206367</v>
+        <v>1.1519400082063671</v>
       </c>
       <c r="V26">
-        <v>3.57030938543588</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>3.5703093854358801</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>55</v>
       </c>
       <c r="B27">
-        <v>2303.608192</v>
+        <v>2303.6081920000001</v>
       </c>
       <c r="C27">
         <v>103973</v>
@@ -2230,22 +2553,22 @@
         <v>5.8</v>
       </c>
       <c r="E27">
-        <v>18.10344828</v>
+        <v>18.103448279999999</v>
       </c>
       <c r="F27">
-        <v>0.868055556</v>
+        <v>0.86805555599999995</v>
       </c>
       <c r="G27">
         <v>2.5</v>
       </c>
       <c r="H27">
-        <v>4024.515493</v>
+        <v>4024.5154929999999</v>
       </c>
       <c r="I27">
         <v>1.076923077</v>
       </c>
       <c r="J27">
-        <v>72.76923076999999</v>
+        <v>72.769230769999993</v>
       </c>
       <c r="K27">
         <v>13.88888889</v>
@@ -2253,31 +2576,29 @@
       <c r="L27">
         <v>2727</v>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Island Park - Wellington Village</t>
-        </is>
+      <c r="M27" t="s">
+        <v>47</v>
       </c>
       <c r="N27">
-        <v>47.99591849313856</v>
+        <v>47.995918493138561</v>
       </c>
       <c r="O27">
-        <v>0.7634279935629372</v>
+        <v>0.76342799356293722</v>
       </c>
       <c r="P27">
-        <v>0.9316949908634262</v>
+        <v>0.93169499086342622</v>
       </c>
       <c r="Q27">
         <v>6.25</v>
       </c>
       <c r="R27">
-        <v>3.604713603615173</v>
+        <v>3.6047136036151728</v>
       </c>
       <c r="S27">
         <v>1.037749043362604</v>
       </c>
       <c r="T27">
-        <v>8.530488307828573</v>
+        <v>8.5304883078285734</v>
       </c>
       <c r="U27">
         <v>1.142667503603475</v>
@@ -2286,7 +2607,7 @@
         <v>3.43568513794163</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>64</v>
       </c>
@@ -2300,45 +2621,43 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>4.755614267</v>
+        <v>4.7556142670000003</v>
       </c>
       <c r="F28">
-        <v>1.042238069</v>
+        <v>1.0422380689999999</v>
       </c>
       <c r="G28">
         <v>2.7</v>
       </c>
       <c r="H28">
-        <v>46.53183419</v>
+        <v>46.531834189999998</v>
       </c>
       <c r="I28">
-        <v>2.956705385</v>
+        <v>2.9567053849999998</v>
       </c>
       <c r="J28">
-        <v>48.36325238</v>
+        <v>48.363252379999999</v>
       </c>
       <c r="K28">
-        <v>20.13165112</v>
+        <v>20.131651120000001</v>
       </c>
       <c r="L28">
         <v>3571</v>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Manotick</t>
-        </is>
+      <c r="M28" t="s">
+        <v>48</v>
       </c>
       <c r="N28">
-        <v>12.47814048646672</v>
+        <v>12.478140486466719</v>
       </c>
       <c r="O28">
-        <v>0.7781512503836436</v>
+        <v>0.77815125038364363</v>
       </c>
       <c r="P28">
         <v>1.020900616612606</v>
       </c>
       <c r="Q28">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R28">
         <v>1.667750171873388</v>
@@ -2347,21 +2666,21 @@
         <v>1.719507308795168</v>
       </c>
       <c r="T28">
-        <v>6.954369301381686</v>
+        <v>6.9543693013816856</v>
       </c>
       <c r="U28">
         <v>1.303879395499604</v>
       </c>
       <c r="V28">
-        <v>3.552789850192782</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>3.5527898501927822</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>65</v>
       </c>
       <c r="B29">
-        <v>457.2895573</v>
+        <v>457.28955730000001</v>
       </c>
       <c r="C29">
         <v>108166</v>
@@ -2370,63 +2689,61 @@
         <v>6.2</v>
       </c>
       <c r="E29">
-        <v>9.803921569</v>
+        <v>9.8039215689999999</v>
       </c>
       <c r="F29">
-        <v>0.6734006729999999</v>
+        <v>0.67340067299999995</v>
       </c>
       <c r="G29">
         <v>2.7</v>
       </c>
       <c r="H29">
-        <v>796.7924104</v>
+        <v>796.79241039999999</v>
       </c>
       <c r="I29">
-        <v>2.797202797</v>
+        <v>2.7972027970000002</v>
       </c>
       <c r="J29">
-        <v>55.59440559</v>
+        <v>55.594405590000001</v>
       </c>
       <c r="K29">
-        <v>26.09427609</v>
+        <v>26.094276090000001</v>
       </c>
       <c r="L29">
         <v>2545</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Merivale Gardens - Grenfell Glen - Pineglen - Country Place</t>
-        </is>
+      <c r="M29" t="s">
+        <v>49</v>
       </c>
       <c r="N29">
         <v>21.38432971360103</v>
       </c>
       <c r="O29">
-        <v>0.7923916894982539</v>
+        <v>0.79239168949825389</v>
       </c>
       <c r="P29">
         <v>0.8206099396180867</v>
       </c>
       <c r="Q29">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R29">
-        <v>2.901345188697397</v>
+        <v>2.9013451886973969</v>
       </c>
       <c r="S29">
         <v>1.672484019953554</v>
       </c>
       <c r="T29">
-        <v>7.456165609078168</v>
+        <v>7.4561656090781678</v>
       </c>
       <c r="U29">
-        <v>1.41654525311793</v>
+        <v>1.4165452531179299</v>
       </c>
       <c r="V29">
-        <v>3.405687786672777</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>3.4056877866727771</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>66</v>
       </c>
@@ -2437,10 +2754,10 @@
         <v>88946</v>
       </c>
       <c r="D30">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="E30">
-        <v>1.470588235</v>
+        <v>1.4705882349999999</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2449,13 +2766,13 @@
         <v>2.7</v>
       </c>
       <c r="H30">
-        <v>8.886538451</v>
+        <v>8.8865384509999998</v>
       </c>
       <c r="I30">
-        <v>7.742998353</v>
+        <v>7.7429983529999999</v>
       </c>
       <c r="J30">
-        <v>23.55848435</v>
+        <v>23.558484350000001</v>
       </c>
       <c r="K30">
         <v>12.24880383</v>
@@ -2463,45 +2780,43 @@
       <c r="L30">
         <v>2953</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Metcalfe</t>
-        </is>
+      <c r="M30" t="s">
+        <v>50</v>
       </c>
       <c r="N30">
-        <v>6.111867004443078</v>
+        <v>6.1118670044430781</v>
       </c>
       <c r="O30">
-        <v>0.7075701760979364</v>
+        <v>0.70757017609793638</v>
       </c>
       <c r="P30">
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R30">
-        <v>0.9487326243688801</v>
+        <v>0.94873262436888006</v>
       </c>
       <c r="S30">
-        <v>2.78262436433666</v>
+        <v>2.7826243643366602</v>
       </c>
       <c r="T30">
-        <v>4.853708309117885</v>
+        <v>4.8537083091178852</v>
       </c>
       <c r="U30">
-        <v>1.088093679280529</v>
+        <v>1.0880936792805289</v>
       </c>
       <c r="V30">
-        <v>3.470263446965078</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>3.4702634469650779</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>67</v>
       </c>
       <c r="B31">
-        <v>26.45934048</v>
+        <v>26.459340480000002</v>
       </c>
       <c r="C31">
         <v>91920</v>
@@ -2510,42 +2825,40 @@
         <v>4.3</v>
       </c>
       <c r="E31">
-        <v>5.507246377</v>
+        <v>5.5072463770000004</v>
       </c>
       <c r="F31">
-        <v>0.27739251</v>
+        <v>0.27739250999999998</v>
       </c>
       <c r="G31">
         <v>2.8</v>
       </c>
       <c r="H31">
-        <v>4.066151076</v>
+        <v>4.0661510759999997</v>
       </c>
       <c r="I31">
         <v>4.736842105</v>
       </c>
       <c r="J31">
-        <v>21.57894737</v>
+        <v>21.578947370000002</v>
       </c>
       <c r="K31">
-        <v>17.3370319</v>
+        <v>17.337031899999999</v>
       </c>
       <c r="L31">
         <v>2964</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Munster - Ashton</t>
-        </is>
+      <c r="M31" t="s">
+        <v>51</v>
       </c>
       <c r="N31">
-        <v>5.143864352799362</v>
+        <v>5.1438643527993619</v>
       </c>
       <c r="O31">
-        <v>0.6334684555795865</v>
+        <v>0.63346845557958653</v>
       </c>
       <c r="P31">
-        <v>0.5266806527678798</v>
+        <v>0.52668065276787979</v>
       </c>
       <c r="Q31">
         <v>7.839999999999999</v>
@@ -2557,7 +2870,7 @@
         <v>2.176428750269578</v>
       </c>
       <c r="T31">
-        <v>4.645314560931261</v>
+        <v>4.6453145609312614</v>
       </c>
       <c r="U31">
         <v>1.238974748285153</v>
@@ -2566,12 +2879,12 @@
         <v>3.47187819930729</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>70</v>
       </c>
       <c r="B32">
-        <v>36.0974421</v>
+        <v>36.097442100000002</v>
       </c>
       <c r="C32">
         <v>93667</v>
@@ -2580,22 +2893,22 @@
         <v>4.8</v>
       </c>
       <c r="E32">
-        <v>3.585657371</v>
+        <v>3.5856573709999999</v>
       </c>
       <c r="F32">
-        <v>0.476190476</v>
+        <v>0.47619047599999997</v>
       </c>
       <c r="G32">
         <v>2.8</v>
       </c>
       <c r="H32">
-        <v>7.570149289</v>
+        <v>7.5701492889999997</v>
       </c>
       <c r="I32">
-        <v>4.618117229</v>
+        <v>4.6181172290000001</v>
       </c>
       <c r="J32">
-        <v>29.8401421</v>
+        <v>29.840142100000001</v>
       </c>
       <c r="K32">
         <v>14.66666667</v>
@@ -2603,40 +2916,38 @@
       <c r="L32">
         <v>2278</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>North Gower - Kars</t>
-        </is>
+      <c r="M32" t="s">
+        <v>52</v>
       </c>
       <c r="N32">
-        <v>6.00811468765369</v>
+        <v>6.0081146876536904</v>
       </c>
       <c r="O32">
-        <v>0.6812412373755872</v>
+        <v>0.68124123737558717</v>
       </c>
       <c r="P32">
-        <v>0.6900655592043411</v>
+        <v>0.69006555920434109</v>
       </c>
       <c r="Q32">
         <v>7.839999999999999</v>
       </c>
       <c r="R32">
-        <v>0.8791044441961895</v>
+        <v>0.87910444419618949</v>
       </c>
       <c r="S32">
         <v>2.148980509218267</v>
       </c>
       <c r="T32">
-        <v>5.462613120110191</v>
+        <v>5.4626131201101913</v>
       </c>
       <c r="U32">
-        <v>1.166331421865228</v>
+        <v>1.1663314218652281</v>
       </c>
       <c r="V32">
-        <v>3.357553719743081</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>3.3575537197430809</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>75</v>
       </c>
@@ -2647,71 +2958,69 @@
         <v>101258</v>
       </c>
       <c r="D33">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="E33">
-        <v>16.37372803</v>
+        <v>16.373728029999999</v>
       </c>
       <c r="F33">
-        <v>1.342615614</v>
+        <v>1.3426156140000001</v>
       </c>
       <c r="G33">
         <v>3</v>
       </c>
       <c r="H33">
-        <v>282.915465</v>
+        <v>282.91546499999998</v>
       </c>
       <c r="I33">
-        <v>4.600694444</v>
+        <v>4.6006944440000002</v>
       </c>
       <c r="J33">
-        <v>45.13888889</v>
+        <v>45.138888889999997</v>
       </c>
       <c r="K33">
-        <v>8.403779214</v>
+        <v>8.4037792140000001</v>
       </c>
       <c r="L33">
         <v>5088</v>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Chapel Hill South</t>
-        </is>
+      <c r="M33" t="s">
+        <v>53</v>
       </c>
       <c r="N33">
         <v>31.76104823522045</v>
       </c>
       <c r="O33">
-        <v>0.7075701760979364</v>
+        <v>0.70757017609793638</v>
       </c>
       <c r="P33">
-        <v>1.158712912675094</v>
+        <v>1.1587129126750939</v>
       </c>
       <c r="Q33">
         <v>9</v>
       </c>
       <c r="R33">
-        <v>2.451656687932746</v>
+        <v>2.4516566879327462</v>
       </c>
       <c r="S33">
-        <v>2.144922945935355</v>
+        <v>2.1449229459353552</v>
       </c>
       <c r="T33">
-        <v>6.718548123664815</v>
+        <v>6.7185481236648146</v>
       </c>
       <c r="U33">
-        <v>0.9244746340003308</v>
+        <v>0.92447463400033081</v>
       </c>
       <c r="V33">
         <v>3.706547102640358</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>76</v>
       </c>
       <c r="B34">
-        <v>1107.68024</v>
+        <v>1107.6802399999999</v>
       </c>
       <c r="C34">
         <v>78504</v>
@@ -2729,30 +3038,28 @@
         <v>2.4</v>
       </c>
       <c r="H34">
-        <v>41.30779044</v>
+        <v>41.307790439999998</v>
       </c>
       <c r="I34">
-        <v>5.416666667</v>
+        <v>5.4166666670000003</v>
       </c>
       <c r="J34">
-        <v>27.70833333</v>
+        <v>27.708333329999999</v>
       </c>
       <c r="K34">
-        <v>17.4584323</v>
+        <v>17.458432299999998</v>
       </c>
       <c r="L34">
         <v>2809</v>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Chatelaine Village</t>
-        </is>
+      <c r="M34" t="s">
+        <v>54</v>
       </c>
       <c r="N34">
-        <v>33.28183047850583</v>
+        <v>33.281830478505832</v>
       </c>
       <c r="O34">
-        <v>0.7923916894982539</v>
+        <v>0.79239168949825389</v>
       </c>
       <c r="P34">
         <v>1.580198515377103</v>
@@ -2767,21 +3074,21 @@
         <v>2.327373340699769</v>
       </c>
       <c r="T34">
-        <v>5.263870565467962</v>
+        <v>5.2638705654679621</v>
       </c>
       <c r="U34">
         <v>1.242005243148077</v>
       </c>
       <c r="V34">
-        <v>3.448551739201578</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>3.4485517392015779</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>81</v>
       </c>
       <c r="B35">
-        <v>39.44474187</v>
+        <v>39.444741870000001</v>
       </c>
       <c r="C35">
         <v>89524</v>
@@ -2793,19 +3100,19 @@
         <v>1.308411215</v>
       </c>
       <c r="F35">
-        <v>0.559701493</v>
+        <v>0.55970149300000005</v>
       </c>
       <c r="G35">
         <v>2.8</v>
       </c>
       <c r="H35">
-        <v>6.269947775</v>
+        <v>6.2699477750000003</v>
       </c>
       <c r="I35">
-        <v>5.154639175</v>
+        <v>5.1546391749999998</v>
       </c>
       <c r="J35">
-        <v>25.94501718</v>
+        <v>25.945017180000001</v>
       </c>
       <c r="K35">
         <v>14.0858209</v>
@@ -2813,45 +3120,43 @@
       <c r="L35">
         <v>2283</v>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Osgoode - Vernon</t>
-        </is>
+      <c r="M35" t="s">
+        <v>55</v>
       </c>
       <c r="N35">
-        <v>6.280504905658462</v>
+        <v>6.2805049056584616</v>
       </c>
       <c r="O35">
-        <v>0.724275869600789</v>
+        <v>0.72427586960078905</v>
       </c>
       <c r="P35">
-        <v>0.7481320023899526</v>
+        <v>0.74813200238995259</v>
       </c>
       <c r="Q35">
         <v>7.839999999999999</v>
       </c>
       <c r="R35">
-        <v>0.7972639234266053</v>
+        <v>0.79726392342660535</v>
       </c>
       <c r="S35">
         <v>2.270383045875739</v>
       </c>
       <c r="T35">
-        <v>5.093625151108</v>
+        <v>5.0936251511080002</v>
       </c>
       <c r="U35">
         <v>1.148782162074472</v>
       </c>
       <c r="V35">
-        <v>3.358505911490235</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>3.3585059114902349</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>82</v>
       </c>
       <c r="B36">
-        <v>4278.535711</v>
+        <v>4278.5357110000004</v>
       </c>
       <c r="C36">
         <v>65072</v>
@@ -2860,36 +3165,34 @@
         <v>8.9</v>
       </c>
       <c r="E36">
-        <v>24.16555407</v>
+        <v>24.165554069999999</v>
       </c>
       <c r="F36">
-        <v>3.263086336</v>
+        <v>3.2630863360000002</v>
       </c>
       <c r="G36">
         <v>2.1</v>
       </c>
       <c r="H36">
-        <v>633.9218217</v>
+        <v>633.92182170000001</v>
       </c>
       <c r="I36">
-        <v>1.140684411</v>
+        <v>1.1406844110000001</v>
       </c>
       <c r="J36">
-        <v>71.22940431000001</v>
+        <v>71.229404310000007</v>
       </c>
       <c r="K36">
-        <v>12.17687075</v>
+        <v>12.176870750000001</v>
       </c>
       <c r="L36">
         <v>3838</v>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Old Ottawa East</t>
-        </is>
+      <c r="M36" t="s">
+        <v>56</v>
       </c>
       <c r="N36">
-        <v>65.41051682260277</v>
+        <v>65.410516822602773</v>
       </c>
       <c r="O36">
         <v>0.9493900066449128</v>
@@ -2901,27 +3204,27 @@
         <v>4.41</v>
       </c>
       <c r="R36">
-        <v>2.802035701891519</v>
+        <v>2.8020357018915192</v>
       </c>
       <c r="S36">
-        <v>1.068028281928901</v>
+        <v>1.0680282819289011</v>
       </c>
       <c r="T36">
-        <v>8.439751436505698</v>
+        <v>8.4397514365056985</v>
       </c>
       <c r="U36">
         <v>1.085535696292373</v>
       </c>
       <c r="V36">
-        <v>3.584104970399453</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>3.5841049703994532</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>83</v>
       </c>
       <c r="B37">
-        <v>4300.573815</v>
+        <v>4300.5738149999997</v>
       </c>
       <c r="C37">
         <v>102300</v>
@@ -2930,68 +3233,66 @@
         <v>7.7</v>
       </c>
       <c r="E37">
-        <v>16.34782609</v>
+        <v>16.347826090000002</v>
       </c>
       <c r="F37">
-        <v>1.93236715</v>
+        <v>1.9323671499999999</v>
       </c>
       <c r="G37">
         <v>2.6</v>
       </c>
       <c r="H37">
-        <v>1090.725243</v>
+        <v>1090.7252430000001</v>
       </c>
       <c r="I37">
-        <v>1.236476043</v>
+        <v>1.2364760429999999</v>
       </c>
       <c r="J37">
-        <v>79.13446677</v>
+        <v>79.134466770000003</v>
       </c>
       <c r="K37">
-        <v>13.20450886</v>
+        <v>13.204508860000001</v>
       </c>
       <c r="L37">
         <v>2990</v>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Old Ottawa South</t>
-        </is>
+      <c r="M37" t="s">
+        <v>57</v>
       </c>
       <c r="N37">
-        <v>65.57876039542072</v>
+        <v>65.578760395420716</v>
       </c>
       <c r="O37">
-        <v>0.8864907251724818</v>
+        <v>0.88649072517248184</v>
       </c>
       <c r="P37">
         <v>1.390096093800713</v>
       </c>
       <c r="Q37">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R37">
-        <v>3.037715364266688</v>
+        <v>3.0377153642666879</v>
       </c>
       <c r="S37">
         <v>1.111969443375131</v>
       </c>
       <c r="T37">
-        <v>8.895755548012771</v>
+        <v>8.8957555480127706</v>
       </c>
       <c r="U37">
-        <v>1.12072225231624</v>
+        <v>1.1207222523162399</v>
       </c>
       <c r="V37">
         <v>3.47567118832443</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>85</v>
       </c>
       <c r="B38">
-        <v>7.710796241</v>
+        <v>7.7107962409999997</v>
       </c>
       <c r="C38">
         <v>81192</v>
@@ -3009,10 +3310,10 @@
         <v>2.6</v>
       </c>
       <c r="H38">
-        <v>0.301904191</v>
+        <v>0.30190419099999999</v>
       </c>
       <c r="I38">
-        <v>5.164319249</v>
+        <v>5.1643192490000001</v>
       </c>
       <c r="J38">
         <v>24.88262911</v>
@@ -3023,110 +3324,106 @@
       <c r="L38">
         <v>2300</v>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Marlborough</t>
-        </is>
+      <c r="M38" t="s">
+        <v>58</v>
       </c>
       <c r="N38">
-        <v>2.776832051277138</v>
+        <v>2.7768320512771378</v>
       </c>
       <c r="O38">
-        <v>0.6989700043360189</v>
+        <v>0.69897000433601886</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R38">
-        <v>-0.5201308581079385</v>
+        <v>-0.52013085810793847</v>
       </c>
       <c r="S38">
-        <v>2.272513861123844</v>
+        <v>2.2725138611238438</v>
       </c>
       <c r="T38">
-        <v>4.988249102641126</v>
+        <v>4.9882491026411264</v>
       </c>
       <c r="U38">
-        <v>1.193360211847612</v>
+        <v>1.1933602118476121</v>
       </c>
       <c r="V38">
-        <v>3.361727836017593</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>3.3617278360175931</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>86</v>
       </c>
       <c r="B39">
-        <v>3375.488227</v>
+        <v>3375.4882269999998</v>
       </c>
       <c r="C39">
         <v>69537</v>
       </c>
       <c r="D39">
-        <v>9.699999999999999</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="E39">
-        <v>26.03648425</v>
+        <v>26.036484250000001</v>
       </c>
       <c r="F39">
-        <v>2.60798696</v>
+        <v>2.6079869599999999</v>
       </c>
       <c r="G39">
         <v>2.7</v>
       </c>
       <c r="H39">
-        <v>2002.73466</v>
+        <v>2002.7346600000001</v>
       </c>
       <c r="I39">
-        <v>9.393063584</v>
+        <v>9.3930635840000001</v>
       </c>
       <c r="J39">
-        <v>26.44508671</v>
+        <v>26.445086710000002</v>
       </c>
       <c r="K39">
-        <v>12.87693562</v>
+        <v>12.876935619999999</v>
       </c>
       <c r="L39">
         <v>4295</v>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Pineview</t>
-        </is>
+      <c r="M39" t="s">
+        <v>59</v>
       </c>
       <c r="N39">
-        <v>58.09895203013562</v>
+        <v>58.098952030135621</v>
       </c>
       <c r="O39">
-        <v>0.9867717342662449</v>
+        <v>0.98677173426624487</v>
       </c>
       <c r="P39">
-        <v>1.614926301724014</v>
+        <v>1.6149263017240141</v>
       </c>
       <c r="Q39">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R39">
-        <v>3.301623413931013</v>
+        <v>3.3016234139310132</v>
       </c>
       <c r="S39">
-        <v>3.064810529869669</v>
+        <v>3.0648105298696691</v>
       </c>
       <c r="T39">
-        <v>5.142478654306696</v>
+        <v>5.1424786543066956</v>
       </c>
       <c r="U39">
         <v>1.109812524385194</v>
       </c>
       <c r="V39">
-        <v>3.632963168167261</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>3.6329631681672612</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>87</v>
       </c>
@@ -3140,54 +3437,52 @@
         <v>6.4</v>
       </c>
       <c r="E40">
-        <v>16.23376623</v>
+        <v>16.233766230000001</v>
       </c>
       <c r="F40">
         <v>1.763224181</v>
       </c>
       <c r="G40">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H40">
-        <v>151.4594354</v>
+        <v>151.45943539999999</v>
       </c>
       <c r="I40">
-        <v>5.415162455</v>
+        <v>5.4151624549999999</v>
       </c>
       <c r="J40">
-        <v>53.79061372</v>
+        <v>53.790613720000003</v>
       </c>
       <c r="K40">
-        <v>26.70025189</v>
+        <v>26.700251890000001</v>
       </c>
       <c r="L40">
         <v>4076</v>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Playfair Park - Lynda Park - Guildwood Estates</t>
-        </is>
+      <c r="M40" t="s">
+        <v>60</v>
       </c>
       <c r="N40">
-        <v>53.68054061762046</v>
+        <v>53.680540617620458</v>
       </c>
       <c r="O40">
-        <v>0.8061799739838872</v>
+        <v>0.80617997398388719</v>
       </c>
       <c r="P40">
         <v>1.327864519068116</v>
       </c>
       <c r="Q40">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R40">
-        <v>2.180296333558701</v>
+        <v>2.1802963335587009</v>
       </c>
       <c r="S40">
-        <v>2.32705016168539</v>
+        <v>2.3270501616853898</v>
       </c>
       <c r="T40">
-        <v>7.334208458995422</v>
+        <v>7.3342084589954224</v>
       </c>
       <c r="U40">
         <v>1.426515358515176</v>
@@ -3196,24 +3491,24 @@
         <v>3.610234175334389</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>88</v>
       </c>
       <c r="B41">
-        <v>2326.446106</v>
+        <v>2326.4461059999999</v>
       </c>
       <c r="C41">
         <v>68338</v>
       </c>
       <c r="D41">
-        <v>8.800000000000001</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="E41">
-        <v>21.39175258</v>
+        <v>21.391752579999999</v>
       </c>
       <c r="F41">
-        <v>2.920560748</v>
+        <v>2.9205607480000002</v>
       </c>
       <c r="G41">
         <v>2.5</v>
@@ -3222,27 +3517,25 @@
         <v>1988.350434</v>
       </c>
       <c r="I41">
-        <v>7.947019868</v>
+        <v>7.9470198679999999</v>
       </c>
       <c r="J41">
-        <v>43.70860927</v>
+        <v>43.708609269999997</v>
       </c>
       <c r="K41">
-        <v>16.0046729</v>
+        <v>16.004672899999999</v>
       </c>
       <c r="L41">
         <v>3848</v>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Qualicum - Redwood Park</t>
-        </is>
+      <c r="M41" t="s">
+        <v>61</v>
       </c>
       <c r="N41">
-        <v>48.23324689464727</v>
+        <v>48.233246894647273</v>
       </c>
       <c r="O41">
-        <v>0.9444826721501687</v>
+        <v>0.94448267215016868</v>
       </c>
       <c r="P41">
         <v>1.708964817660094</v>
@@ -3251,27 +3544,27 @@
         <v>6.25</v>
       </c>
       <c r="R41">
-        <v>3.298492928421602</v>
+        <v>3.2984929284216018</v>
       </c>
       <c r="S41">
-        <v>2.81904591448951</v>
+        <v>2.8190459144895099</v>
       </c>
       <c r="T41">
-        <v>6.611248692191211</v>
+        <v>6.6112486921912108</v>
       </c>
       <c r="U41">
-        <v>1.204246802555334</v>
+        <v>1.2042468025553339</v>
       </c>
       <c r="V41">
-        <v>3.585235063365775</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>3.5852350633657748</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>90</v>
       </c>
       <c r="B42">
-        <v>1383.864056</v>
+        <v>1383.8640559999999</v>
       </c>
       <c r="C42">
         <v>62992</v>
@@ -3280,63 +3573,61 @@
         <v>6.8</v>
       </c>
       <c r="E42">
-        <v>27.97029703</v>
+        <v>27.970297030000001</v>
       </c>
       <c r="F42">
-        <v>9.539842873</v>
+        <v>9.5398428729999996</v>
       </c>
       <c r="G42">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H42">
         <v>1903.861459</v>
       </c>
       <c r="I42">
-        <v>5.579399142</v>
+        <v>5.5793991419999998</v>
       </c>
       <c r="J42">
-        <v>50.42918455</v>
+        <v>50.429184550000002</v>
       </c>
       <c r="K42">
-        <v>19.97755331</v>
+        <v>19.977553310000001</v>
       </c>
       <c r="L42">
         <v>3441</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Riverside Park</t>
-        </is>
+      <c r="M42" t="s">
+        <v>62</v>
       </c>
       <c r="N42">
-        <v>37.20032333192817</v>
+        <v>37.200323331928168</v>
       </c>
       <c r="O42">
-        <v>0.8325089127062363</v>
+        <v>0.83250891270623628</v>
       </c>
       <c r="P42">
         <v>3.088663606319082</v>
       </c>
       <c r="Q42">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R42">
-        <v>3.279635342272765</v>
+        <v>3.2796353422727651</v>
       </c>
       <c r="S42">
-        <v>2.362075177042424</v>
+        <v>2.3620751770424242</v>
       </c>
       <c r="T42">
-        <v>7.101350896132369</v>
+        <v>7.1013508961323693</v>
       </c>
       <c r="U42">
-        <v>1.300542298252744</v>
+        <v>1.3005422982527439</v>
       </c>
       <c r="V42">
-        <v>3.53668467262093</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>3.5366846726209298</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>93</v>
       </c>
@@ -3353,65 +3644,63 @@
         <v>25.89498807</v>
       </c>
       <c r="F43">
-        <v>2.81416788</v>
+        <v>2.8141678799999998</v>
       </c>
       <c r="G43">
         <v>2.6</v>
       </c>
       <c r="H43">
-        <v>799.4906279</v>
+        <v>799.49062790000005</v>
       </c>
       <c r="I43">
-        <v>5.252317199</v>
+        <v>5.2523171990000002</v>
       </c>
       <c r="J43">
-        <v>50.56642636</v>
+        <v>50.566426360000001</v>
       </c>
       <c r="K43">
-        <v>24.06598738</v>
+        <v>24.065987379999999</v>
       </c>
       <c r="L43">
         <v>2848</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Rothwell Heights - Beacon Hill North</t>
-        </is>
+      <c r="M43" t="s">
+        <v>63</v>
       </c>
       <c r="N43">
-        <v>41.62511304489154</v>
+        <v>41.625113044891542</v>
       </c>
       <c r="O43">
-        <v>0.8808135922807914</v>
+        <v>0.88081359228079137</v>
       </c>
       <c r="P43">
         <v>1.677548175165172</v>
       </c>
       <c r="Q43">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R43">
-        <v>2.902813377056399</v>
+        <v>2.9028133770563991</v>
       </c>
       <c r="S43">
-        <v>2.291793445971953</v>
+        <v>2.2917934459719529</v>
       </c>
       <c r="T43">
-        <v>7.111007408236895</v>
+        <v>7.1110074082368948</v>
       </c>
       <c r="U43">
-        <v>1.381403684625001</v>
+        <v>1.3814036846250011</v>
       </c>
       <c r="V43">
-        <v>3.454539984964819</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>3.4545399849648191</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>97</v>
       </c>
       <c r="B44">
-        <v>1333.329609</v>
+        <v>1333.3296089999999</v>
       </c>
       <c r="C44">
         <v>73679</v>
@@ -3429,13 +3718,13 @@
         <v>2.5</v>
       </c>
       <c r="H44">
-        <v>1671.862943</v>
+        <v>1671.8629430000001</v>
       </c>
       <c r="I44">
-        <v>5.023923445</v>
+        <v>5.0239234450000003</v>
       </c>
       <c r="J44">
-        <v>43.54066986</v>
+        <v>43.540669860000001</v>
       </c>
       <c r="K44">
         <v>19.85815603</v>
@@ -3443,45 +3732,43 @@
       <c r="L44">
         <v>3877</v>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>South Keys - Greenboro West</t>
-        </is>
+      <c r="M44" t="s">
+        <v>64</v>
       </c>
       <c r="N44">
-        <v>36.514786169441</v>
+        <v>36.514786169441003</v>
       </c>
       <c r="O44">
-        <v>0.9084850188786497</v>
+        <v>0.90848501887864974</v>
       </c>
       <c r="P44">
-        <v>1.754116038635985</v>
+        <v>1.7541160386359851</v>
       </c>
       <c r="Q44">
         <v>6.25</v>
       </c>
       <c r="R44">
-        <v>3.223200671704343</v>
+        <v>3.2232006717043431</v>
       </c>
       <c r="S44">
         <v>2.241411038832458</v>
       </c>
       <c r="T44">
-        <v>6.598535432957831</v>
+        <v>6.5985354329578314</v>
       </c>
       <c r="U44">
         <v>1.297938918722513</v>
       </c>
       <c r="V44">
-        <v>3.58849580100721</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>3.5884958010072099</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>99</v>
       </c>
       <c r="B45">
-        <v>2156.178775</v>
+        <v>2156.1787749999999</v>
       </c>
       <c r="C45">
         <v>68280</v>
@@ -3490,39 +3777,37 @@
         <v>8.1</v>
       </c>
       <c r="E45">
-        <v>27.87234043</v>
+        <v>27.872340430000001</v>
       </c>
       <c r="F45">
-        <v>3.597883598</v>
+        <v>3.5978835980000001</v>
       </c>
       <c r="G45">
         <v>2.5</v>
       </c>
       <c r="H45">
-        <v>393.360022</v>
+        <v>393.36002200000001</v>
       </c>
       <c r="I45">
-        <v>7.707129094</v>
+        <v>7.7071290939999999</v>
       </c>
       <c r="J45">
         <v>26.7822736</v>
       </c>
       <c r="K45">
-        <v>17.56613757</v>
+        <v>17.566137569999999</v>
       </c>
       <c r="L45">
         <v>3688</v>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Tanglewood</t>
-        </is>
+      <c r="M45" t="s">
+        <v>65</v>
       </c>
       <c r="N45">
-        <v>46.43467212116394</v>
+        <v>46.434672121163942</v>
       </c>
       <c r="O45">
-        <v>0.9084850188786497</v>
+        <v>0.90848501887864974</v>
       </c>
       <c r="P45">
         <v>1.896808793210323</v>
@@ -3531,27 +3816,27 @@
         <v>6.25</v>
       </c>
       <c r="R45">
-        <v>2.594790219571505</v>
+        <v>2.5947902195715051</v>
       </c>
       <c r="S45">
-        <v>2.776171661479167</v>
+        <v>2.7761716614791672</v>
       </c>
       <c r="T45">
-        <v>5.175159282572857</v>
+        <v>5.1751592825728574</v>
       </c>
       <c r="U45">
-        <v>1.244676279626285</v>
+        <v>1.2446762796262849</v>
       </c>
       <c r="V45">
-        <v>3.566790912381592</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>3.5667909123815922</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>100</v>
       </c>
       <c r="B46">
-        <v>2825.563579</v>
+        <v>2825.5635790000001</v>
       </c>
       <c r="C46">
         <v>84293</v>
@@ -3560,7 +3845,7 @@
         <v>6.7</v>
       </c>
       <c r="E46">
-        <v>18.0778032</v>
+        <v>18.077803200000002</v>
       </c>
       <c r="F46">
         <v>1.53531218</v>
@@ -3569,30 +3854,28 @@
         <v>2.5</v>
       </c>
       <c r="H46">
-        <v>508.4858793</v>
+        <v>508.48587930000002</v>
       </c>
       <c r="I46">
         <v>3.448275862</v>
       </c>
       <c r="J46">
-        <v>52.73833671</v>
+        <v>52.738336709999999</v>
       </c>
       <c r="K46">
-        <v>21.06339468</v>
+        <v>21.063394679999998</v>
       </c>
       <c r="L46">
         <v>3062</v>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Trend-Arlington</t>
-        </is>
+      <c r="M46" t="s">
+        <v>66</v>
       </c>
       <c r="N46">
-        <v>53.15603050454389</v>
+        <v>53.156030504543892</v>
       </c>
       <c r="O46">
-        <v>0.8260748027008264</v>
+        <v>0.82607480270082645</v>
       </c>
       <c r="P46">
         <v>1.239077148526273</v>
@@ -3601,7 +3884,7 @@
         <v>6.25</v>
       </c>
       <c r="R46">
-        <v>2.706278897028202</v>
+        <v>2.7062788970282021</v>
       </c>
       <c r="S46">
         <v>1.856953381751949</v>
@@ -3613,10 +3896,10 @@
         <v>1.323528365519149</v>
       </c>
       <c r="V46">
-        <v>3.486005186362242</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>3.4860051863622421</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>106</v>
       </c>
@@ -3627,25 +3910,25 @@
         <v>53028</v>
       </c>
       <c r="D47">
-        <v>9.199999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="E47">
         <v>31.62134945</v>
       </c>
       <c r="F47">
-        <v>5.325185509</v>
+        <v>5.3251855089999998</v>
       </c>
       <c r="G47">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H47">
-        <v>1065.653888</v>
+        <v>1065.6538880000001</v>
       </c>
       <c r="I47">
         <v>12.41776316</v>
       </c>
       <c r="J47">
-        <v>36.34868421</v>
+        <v>36.348684210000002</v>
       </c>
       <c r="K47">
         <v>18.11436054</v>
@@ -3653,45 +3936,43 @@
       <c r="L47">
         <v>4094</v>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Whitehaven - Queensway Terrace North</t>
-        </is>
+      <c r="M47" t="s">
+        <v>67</v>
       </c>
       <c r="N47">
-        <v>59.90160775805604</v>
+        <v>59.901607758056038</v>
       </c>
       <c r="O47">
-        <v>0.9637878273455552</v>
+        <v>0.96378782734555524</v>
       </c>
       <c r="P47">
-        <v>2.307636346784302</v>
+        <v>2.3076363467843022</v>
       </c>
       <c r="Q47">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R47">
-        <v>3.027616173790662</v>
+        <v>3.0276161737906619</v>
       </c>
       <c r="S47">
-        <v>3.523884668941366</v>
+        <v>3.5238846689413661</v>
       </c>
       <c r="T47">
-        <v>6.028986997000408</v>
+        <v>6.0289869970004082</v>
       </c>
       <c r="U47">
         <v>1.258023007492765</v>
       </c>
       <c r="V47">
-        <v>3.612147838326487</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>3.6121478383264871</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>108</v>
       </c>
       <c r="B48">
-        <v>2547.413764</v>
+        <v>2547.4137639999999</v>
       </c>
       <c r="C48">
         <v>74643</v>
@@ -3700,63 +3981,61 @@
         <v>8.6</v>
       </c>
       <c r="E48">
-        <v>24.29149798</v>
+        <v>24.291497979999999</v>
       </c>
       <c r="F48">
-        <v>3.958587089</v>
+        <v>3.9585870889999999</v>
       </c>
       <c r="G48">
         <v>2.7</v>
       </c>
       <c r="H48">
-        <v>635.0704065</v>
+        <v>635.07040649999999</v>
       </c>
       <c r="I48">
-        <v>8.581644815000001</v>
+        <v>8.5816448150000006</v>
       </c>
       <c r="J48">
         <v>37.06793802</v>
       </c>
       <c r="K48">
-        <v>17.46804626</v>
+        <v>17.468046260000001</v>
       </c>
       <c r="L48">
         <v>4371</v>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Woodvale - Craig Henry - Manordale - Estates of Arlington Woods</t>
-        </is>
+      <c r="M48" t="s">
+        <v>68</v>
       </c>
       <c r="N48">
-        <v>50.47191064344602</v>
+        <v>50.471910643446023</v>
       </c>
       <c r="O48">
-        <v>0.9344984512435677</v>
+        <v>0.93449845124356767</v>
       </c>
       <c r="P48">
-        <v>1.989619835295175</v>
+        <v>1.9896198352951751</v>
       </c>
       <c r="Q48">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R48">
-        <v>2.802821875621776</v>
+        <v>2.8028218756217762</v>
       </c>
       <c r="S48">
-        <v>2.929444455011906</v>
+        <v>2.9294444550119061</v>
       </c>
       <c r="T48">
-        <v>6.088344439993519</v>
+        <v>6.0883444399935192</v>
       </c>
       <c r="U48">
         <v>1.242244333377315</v>
       </c>
       <c r="V48">
-        <v>3.640580806489653</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>3.6405808064896532</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>901</v>
       </c>
@@ -3770,16 +4049,16 @@
         <v>12.6</v>
       </c>
       <c r="E49">
-        <v>36.20457604</v>
+        <v>36.204576039999999</v>
       </c>
       <c r="F49">
-        <v>14.00651466</v>
+        <v>14.006514660000001</v>
       </c>
       <c r="G49">
         <v>2.7</v>
       </c>
       <c r="H49">
-        <v>2015.01006</v>
+        <v>2015.0100600000001</v>
       </c>
       <c r="I49">
         <v>10.73684211</v>
@@ -3793,40 +4072,38 @@
       <c r="L49">
         <v>6105</v>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Bayshore - Belltown</t>
-        </is>
+      <c r="M49" t="s">
+        <v>69</v>
       </c>
       <c r="N49">
-        <v>75.68257839159551</v>
+        <v>75.682578391595513</v>
       </c>
       <c r="O49">
-        <v>1.100370545117563</v>
+        <v>1.1003705451175629</v>
       </c>
       <c r="P49">
-        <v>3.742527843583799</v>
+        <v>3.7425278435837992</v>
       </c>
       <c r="Q49">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R49">
-        <v>3.304277218711164</v>
+        <v>3.3042772187111642</v>
       </c>
       <c r="S49">
-        <v>3.276712088359305</v>
+        <v>3.2767120883593051</v>
       </c>
       <c r="T49">
-        <v>6.341177045312644</v>
+        <v>6.3411770453126444</v>
       </c>
       <c r="U49">
         <v>1.052773708994611</v>
       </c>
       <c r="V49">
-        <v>3.785685668280901</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>3.7856856682809008</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>902</v>
       </c>
@@ -3840,63 +4117,61 @@
         <v>5.5</v>
       </c>
       <c r="E50">
-        <v>17.03577513</v>
+        <v>17.035775130000001</v>
       </c>
       <c r="F50">
-        <v>3.20855615</v>
+        <v>3.2085561500000002</v>
       </c>
       <c r="G50">
         <v>2.4</v>
       </c>
       <c r="H50">
-        <v>246.9014227</v>
+        <v>246.90142270000001</v>
       </c>
       <c r="I50">
-        <v>4.748201439</v>
+        <v>4.7482014389999998</v>
       </c>
       <c r="J50">
-        <v>45.17985612</v>
+        <v>45.179856119999997</v>
       </c>
       <c r="K50">
-        <v>18.65443425</v>
+        <v>18.654434250000001</v>
       </c>
       <c r="L50">
         <v>2569</v>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Beaverbrook</t>
-        </is>
+      <c r="M50" t="s">
+        <v>70</v>
       </c>
       <c r="N50">
-        <v>47.99452097896175</v>
+        <v>47.994520978961752</v>
       </c>
       <c r="O50">
-        <v>0.7403626894942439</v>
+        <v>0.74036268949424389</v>
       </c>
       <c r="P50">
-        <v>1.791244302154232</v>
+        <v>1.7912443021542319</v>
       </c>
       <c r="Q50">
         <v>5.76</v>
       </c>
       <c r="R50">
-        <v>2.392523592438936</v>
+        <v>2.3925235924389359</v>
       </c>
       <c r="S50">
-        <v>2.17903681451232</v>
+        <v>2.1790368145123198</v>
       </c>
       <c r="T50">
-        <v>6.721596247916115</v>
+        <v>6.7215962479161151</v>
       </c>
       <c r="U50">
-        <v>1.270782082332682</v>
+        <v>1.2707820823326821</v>
       </c>
       <c r="V50">
-        <v>3.409764104266346</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>3.4097641042663458</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>903</v>
       </c>
@@ -3910,68 +4185,66 @@
         <v>7.6</v>
       </c>
       <c r="E51">
-        <v>23.57080035</v>
+        <v>23.570800349999999</v>
       </c>
       <c r="F51">
         <v>2.33293792</v>
       </c>
       <c r="G51">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H51">
-        <v>1642.038831</v>
+        <v>1642.0388310000001</v>
       </c>
       <c r="I51">
-        <v>6.201550388</v>
+        <v>6.2015503880000002</v>
       </c>
       <c r="J51">
-        <v>56.82170543</v>
+        <v>56.821705430000002</v>
       </c>
       <c r="K51">
-        <v>18.62396204</v>
+        <v>18.623962039999999</v>
       </c>
       <c r="L51">
         <v>3720</v>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Billings Bridge - Alta Vista</t>
-        </is>
+      <c r="M51" t="s">
+        <v>71</v>
       </c>
       <c r="N51">
         <v>45.13804316759866</v>
       </c>
       <c r="O51">
-        <v>0.8808135922807914</v>
+        <v>0.88081359228079137</v>
       </c>
       <c r="P51">
         <v>1.527395796773056</v>
       </c>
       <c r="Q51">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R51">
         <v>3.21538342311815</v>
       </c>
       <c r="S51">
-        <v>2.490291225539696</v>
+        <v>2.4902912255396958</v>
       </c>
       <c r="T51">
-        <v>7.538017340786634</v>
+        <v>7.5380173407866344</v>
       </c>
       <c r="U51">
         <v>1.270072077776746</v>
       </c>
       <c r="V51">
-        <v>3.570542939881897</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>3.5705429398818969</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>904</v>
       </c>
       <c r="B52">
-        <v>2743.225459</v>
+        <v>2743.2254589999998</v>
       </c>
       <c r="C52">
         <v>78772</v>
@@ -3980,45 +4253,43 @@
         <v>6</v>
       </c>
       <c r="E52">
-        <v>25.52910053</v>
+        <v>25.529100530000001</v>
       </c>
       <c r="F52">
-        <v>1.542257866</v>
+        <v>1.5422578659999999</v>
       </c>
       <c r="G52">
         <v>2.6</v>
       </c>
       <c r="H52">
-        <v>486.3682893</v>
+        <v>486.36828930000001</v>
       </c>
       <c r="I52">
-        <v>7.859733978</v>
+        <v>7.8597339780000004</v>
       </c>
       <c r="J52">
-        <v>37.60580411</v>
+        <v>37.605804110000001</v>
       </c>
       <c r="K52">
-        <v>19.0006169</v>
+        <v>19.000616900000001</v>
       </c>
       <c r="L52">
         <v>3067</v>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Blackburn Hamlet</t>
-        </is>
+      <c r="M52" t="s">
+        <v>72</v>
       </c>
       <c r="N52">
-        <v>52.37580986486032</v>
+        <v>52.375809864860322</v>
       </c>
       <c r="O52">
-        <v>0.7781512503836436</v>
+        <v>0.77815125038364363</v>
       </c>
       <c r="P52">
-        <v>1.241876751533742</v>
+        <v>1.2418767515337421</v>
       </c>
       <c r="Q52">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R52">
         <v>2.686965251645085</v>
@@ -4027,21 +4298,21 @@
         <v>2.803521709921291</v>
       </c>
       <c r="T52">
-        <v>6.132357141426126</v>
+        <v>6.1323571414261258</v>
       </c>
       <c r="U52">
         <v>1.278767701580017</v>
       </c>
       <c r="V52">
-        <v>3.486713775982485</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>3.4867137759824849</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>905</v>
       </c>
       <c r="B53">
-        <v>2813.339173</v>
+        <v>2813.3391729999998</v>
       </c>
       <c r="C53">
         <v>71291</v>
@@ -4053,65 +4324,63 @@
         <v>19.93865031</v>
       </c>
       <c r="F53">
-        <v>1.307639367</v>
+        <v>1.3076393669999999</v>
       </c>
       <c r="G53">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H53">
-        <v>514.6493822</v>
+        <v>514.64938219999999</v>
       </c>
       <c r="I53">
-        <v>5.314685315</v>
+        <v>5.3146853150000002</v>
       </c>
       <c r="J53">
         <v>46.15384615</v>
       </c>
       <c r="K53">
-        <v>26.63454921</v>
+        <v>26.634549209999999</v>
       </c>
       <c r="L53">
         <v>3152</v>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Borden Farm - Fisher Glen</t>
-        </is>
+      <c r="M53" t="s">
+        <v>73</v>
       </c>
       <c r="N53">
-        <v>53.04091979783156</v>
+        <v>53.040919797831563</v>
       </c>
       <c r="O53">
-        <v>0.8512583487190752</v>
+        <v>0.85125834871907524</v>
       </c>
       <c r="P53">
         <v>1.143520601913232</v>
       </c>
       <c r="Q53">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R53">
-        <v>2.711511455772513</v>
+        <v>2.7115114557725128</v>
       </c>
       <c r="S53">
-        <v>2.305360126964982</v>
+        <v>2.3053601269649819</v>
       </c>
       <c r="T53">
-        <v>6.793662204584505</v>
+        <v>6.7936622045845052</v>
       </c>
       <c r="U53">
-        <v>1.425445350744793</v>
+        <v>1.4254453507447931</v>
       </c>
       <c r="V53">
-        <v>3.498586208817518</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>3.4985862088175179</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>906</v>
       </c>
       <c r="B54">
-        <v>3017.323199</v>
+        <v>3017.3231989999999</v>
       </c>
       <c r="C54">
         <v>43569</v>
@@ -4123,7 +4392,7 @@
         <v>34.03846154</v>
       </c>
       <c r="F54">
-        <v>4.941176471</v>
+        <v>4.9411764710000003</v>
       </c>
       <c r="G54">
         <v>1.8</v>
@@ -4135,7 +4404,7 @@
         <v>12.71428571</v>
       </c>
       <c r="J54">
-        <v>37.42857143</v>
+        <v>37.428571429999998</v>
       </c>
       <c r="K54">
         <v>24</v>
@@ -4143,16 +4412,14 @@
       <c r="L54">
         <v>2705</v>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Britannia Village</t>
-        </is>
+      <c r="M54" t="s">
+        <v>74</v>
       </c>
       <c r="N54">
-        <v>54.93016656628669</v>
+        <v>54.930166566286687</v>
       </c>
       <c r="O54">
-        <v>0.9777236052888477</v>
+        <v>0.97772360528884772</v>
       </c>
       <c r="P54">
         <v>2.222875720997465</v>
@@ -4167,21 +4434,21 @@
         <v>3.565709706355805</v>
       </c>
       <c r="T54">
-        <v>6.117889458792141</v>
+        <v>6.1178894587921411</v>
       </c>
       <c r="U54">
-        <v>1.380211241711606</v>
+        <v>1.3802112417116059</v>
       </c>
       <c r="V54">
         <v>3.432167269442588</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>907</v>
       </c>
       <c r="B55">
-        <v>1671.781126</v>
+        <v>1671.7811260000001</v>
       </c>
       <c r="C55">
         <v>98413</v>
@@ -4199,13 +4466,13 @@
         <v>3.2</v>
       </c>
       <c r="H55">
-        <v>2721.87361</v>
+        <v>2721.8736100000001</v>
       </c>
       <c r="I55">
-        <v>3.965014577</v>
+        <v>3.9650145769999998</v>
       </c>
       <c r="J55">
-        <v>53.64431487</v>
+        <v>53.644314870000002</v>
       </c>
       <c r="K55">
         <v>7.190370605</v>
@@ -4213,16 +4480,14 @@
       <c r="L55">
         <v>2790</v>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Brookside - Briarbrook - Morgan's Grant</t>
-        </is>
+      <c r="M55" t="s">
+        <v>75</v>
       </c>
       <c r="N55">
-        <v>40.88742014360896</v>
+        <v>40.887420143608963</v>
       </c>
       <c r="O55">
-        <v>0.8195439355418687</v>
+        <v>0.81954393554186866</v>
       </c>
       <c r="P55">
         <v>1.989522905874672</v>
@@ -4231,27 +4496,27 @@
         <v>10.24</v>
       </c>
       <c r="R55">
-        <v>3.434867954903332</v>
+        <v>3.4348679549033321</v>
       </c>
       <c r="S55">
-        <v>1.991234435469616</v>
+        <v>1.9912344354696161</v>
       </c>
       <c r="T55">
-        <v>7.324227936786238</v>
+        <v>7.3242279367862384</v>
       </c>
       <c r="U55">
-        <v>0.8567512753006183</v>
+        <v>0.85675127530061834</v>
       </c>
       <c r="V55">
         <v>3.445604203273597</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>908</v>
       </c>
       <c r="B56">
-        <v>4111.862608</v>
+        <v>4111.8626080000004</v>
       </c>
       <c r="C56">
         <v>54686</v>
@@ -4272,56 +4537,54 @@
         <v>15776.20796</v>
       </c>
       <c r="I56">
-        <v>4.270986745</v>
+        <v>4.2709867450000001</v>
       </c>
       <c r="J56">
-        <v>61.8556701</v>
+        <v>61.855670099999998</v>
       </c>
       <c r="K56">
-        <v>15.05376344</v>
+        <v>15.053763440000001</v>
       </c>
       <c r="L56">
         <v>5385</v>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Byward Market</t>
-        </is>
+      <c r="M56" t="s">
+        <v>76</v>
       </c>
       <c r="N56">
-        <v>64.12380687389046</v>
+        <v>64.123806873890459</v>
       </c>
       <c r="O56">
         <v>0.7323937598229685</v>
       </c>
       <c r="P56">
-        <v>1.594222216944677</v>
+        <v>1.5942222169446769</v>
       </c>
       <c r="Q56">
         <v>2.25</v>
       </c>
       <c r="R56">
-        <v>4.198002622450406</v>
+        <v>4.1980026224504057</v>
       </c>
       <c r="S56">
         <v>2.066636577872365</v>
       </c>
       <c r="T56">
-        <v>7.864837576199523</v>
+        <v>7.8648375761995233</v>
       </c>
       <c r="U56">
-        <v>1.177645087099486</v>
+        <v>1.1776450870994859</v>
       </c>
       <c r="V56">
-        <v>3.731185707634</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>3.7311857076339998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>909</v>
       </c>
       <c r="B57">
-        <v>1189.254466</v>
+        <v>1189.2544660000001</v>
       </c>
       <c r="C57">
         <v>99174</v>
@@ -4330,10 +4593,10 @@
         <v>4.8</v>
       </c>
       <c r="E57">
-        <v>23.0964467</v>
+        <v>23.096446700000001</v>
       </c>
       <c r="F57">
-        <v>1.19205298</v>
+        <v>1.1920529799999999</v>
       </c>
       <c r="G57">
         <v>3</v>
@@ -4342,30 +4605,28 @@
         <v>100.6009517</v>
       </c>
       <c r="I57">
-        <v>3.677058353</v>
+        <v>3.6770583530000001</v>
       </c>
       <c r="J57">
-        <v>39.80815348</v>
+        <v>39.808153480000001</v>
       </c>
       <c r="K57">
-        <v>7.637969095</v>
+        <v>7.6379690949999999</v>
       </c>
       <c r="L57">
         <v>4558</v>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Cardinal Creek</t>
-        </is>
+      <c r="M57" t="s">
+        <v>77</v>
       </c>
       <c r="N57">
-        <v>34.48556895282431</v>
+        <v>34.485568952824309</v>
       </c>
       <c r="O57">
-        <v>0.6812412373755872</v>
+        <v>0.68124123737558717</v>
       </c>
       <c r="P57">
-        <v>1.091811787809602</v>
+        <v>1.0918117878096021</v>
       </c>
       <c r="Q57">
         <v>9</v>
@@ -4377,16 +4638,16 @@
         <v>1.917565736291718</v>
       </c>
       <c r="T57">
-        <v>6.30937029187541</v>
+        <v>6.3093702918754104</v>
       </c>
       <c r="U57">
-        <v>0.8829778967843379</v>
+        <v>0.88297789678433791</v>
       </c>
       <c r="V57">
-        <v>3.658774320844357</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>3.6587743208443571</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>910</v>
       </c>
@@ -4400,39 +4661,37 @@
         <v>6.5</v>
       </c>
       <c r="E58">
-        <v>27.1076524</v>
+        <v>27.107652399999999</v>
       </c>
       <c r="F58">
-        <v>2.865013774</v>
+        <v>2.8650137739999999</v>
       </c>
       <c r="G58">
         <v>2</v>
       </c>
       <c r="H58">
-        <v>1774.767896</v>
+        <v>1774.7678960000001</v>
       </c>
       <c r="I58">
-        <v>6.216505895</v>
+        <v>6.2165058950000001</v>
       </c>
       <c r="J58">
-        <v>47.90996785</v>
+        <v>47.909967850000001</v>
       </c>
       <c r="K58">
-        <v>27.82369146</v>
+        <v>27.823691459999999</v>
       </c>
       <c r="L58">
         <v>2709</v>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Carlingwood West - Glabar Park - McKellar Heights</t>
-        </is>
+      <c r="M58" t="s">
+        <v>78</v>
       </c>
       <c r="N58">
-        <v>55.25119881052356</v>
+        <v>55.251198810523562</v>
       </c>
       <c r="O58">
-        <v>0.8129133566428556</v>
+        <v>0.81291335664285558</v>
       </c>
       <c r="P58">
         <v>1.692635156789555</v>
@@ -4447,21 +4706,21 @@
         <v>2.493292180030251</v>
       </c>
       <c r="T58">
-        <v>6.921702669863825</v>
+        <v>6.9217026698638247</v>
       </c>
       <c r="U58">
         <v>1.44441474874567</v>
       </c>
       <c r="V58">
-        <v>3.432809005033168</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>3.4328090050331679</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>911</v>
       </c>
       <c r="B59">
-        <v>37.19686013</v>
+        <v>37.196860129999997</v>
       </c>
       <c r="C59">
         <v>107435</v>
@@ -4470,7 +4729,7 @@
         <v>5.4</v>
       </c>
       <c r="E59">
-        <v>6.310679612</v>
+        <v>6.3106796120000004</v>
       </c>
       <c r="F59">
         <v>1.726726727</v>
@@ -4479,13 +4738,13 @@
         <v>2.8</v>
       </c>
       <c r="H59">
-        <v>20.71398402</v>
+        <v>20.713984020000002</v>
       </c>
       <c r="I59">
-        <v>4.109589041</v>
+        <v>4.1095890410000004</v>
       </c>
       <c r="J59">
-        <v>39.5890411</v>
+        <v>39.589041100000003</v>
       </c>
       <c r="K59">
         <v>13.44853494</v>
@@ -4493,13 +4752,11 @@
       <c r="L59">
         <v>1914</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Carp</t>
-        </is>
+      <c r="M59" t="s">
+        <v>79</v>
       </c>
       <c r="N59">
-        <v>6.098922866375668</v>
+        <v>6.0989228663756681</v>
       </c>
       <c r="O59">
         <v>0.7323937598229685</v>
@@ -4511,83 +4768,81 @@
         <v>7.839999999999999</v>
       </c>
       <c r="R59">
-        <v>1.31626363687021</v>
+        <v>1.3162636368702101</v>
       </c>
       <c r="S59">
-        <v>2.027212135174807</v>
+        <v>2.0272121351748069</v>
       </c>
       <c r="T59">
-        <v>6.291982287006219</v>
+        <v>6.2919822870062188</v>
       </c>
       <c r="U59">
-        <v>1.128674975629926</v>
+        <v>1.1286749756299259</v>
       </c>
       <c r="V59">
-        <v>3.281941933440825</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>3.2819419334408249</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>912</v>
       </c>
       <c r="B60">
-        <v>2506.463574</v>
+        <v>2506.4635739999999</v>
       </c>
       <c r="C60">
         <v>61156</v>
       </c>
       <c r="D60">
-        <v>9.300000000000001</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="E60">
-        <v>26.78571429</v>
+        <v>26.785714290000001</v>
       </c>
       <c r="F60">
         <v>2.863534676</v>
       </c>
       <c r="G60">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H60">
-        <v>3046.783104</v>
+        <v>3046.7831040000001</v>
       </c>
       <c r="I60">
-        <v>9.772535805</v>
+        <v>9.7725358050000004</v>
       </c>
       <c r="J60">
         <v>38.41617523</v>
       </c>
       <c r="K60">
-        <v>18.1655481</v>
+        <v>18.165548099999999</v>
       </c>
       <c r="L60">
         <v>4926</v>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Carson Grove - Carson Meadows</t>
-        </is>
+      <c r="M60" t="s">
+        <v>80</v>
       </c>
       <c r="N60">
-        <v>50.0645940161308</v>
+        <v>50.064594016130798</v>
       </c>
       <c r="O60">
-        <v>0.9684829485539351</v>
+        <v>0.96848294855393513</v>
       </c>
       <c r="P60">
         <v>1.692198178701301</v>
       </c>
       <c r="Q60">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R60">
         <v>3.48384153853881</v>
       </c>
       <c r="S60">
-        <v>3.126105533247398</v>
+        <v>3.1261055332473981</v>
       </c>
       <c r="T60">
-        <v>6.198078349779067</v>
+        <v>6.1980783497790668</v>
       </c>
       <c r="U60">
         <v>1.259248506146678</v>
@@ -4596,12 +4851,12 @@
         <v>3.692494407503085</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>913</v>
       </c>
       <c r="B61">
-        <v>2798.086561</v>
+        <v>2798.0865610000001</v>
       </c>
       <c r="C61">
         <v>92012</v>
@@ -4610,10 +4865,10 @@
         <v>6.6</v>
       </c>
       <c r="E61">
-        <v>21.78988327</v>
+        <v>21.789883270000001</v>
       </c>
       <c r="F61">
-        <v>3.017444602</v>
+        <v>3.0174446019999999</v>
       </c>
       <c r="G61">
         <v>2.7</v>
@@ -4622,10 +4877,10 @@
         <v>133.5060632</v>
       </c>
       <c r="I61">
-        <v>3.948497854</v>
+        <v>3.9484978540000002</v>
       </c>
       <c r="J61">
-        <v>47.98283262</v>
+        <v>47.982832620000003</v>
       </c>
       <c r="K61">
         <v>13.67279585</v>
@@ -4633,40 +4888,38 @@
       <c r="L61">
         <v>3953</v>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Chapel Hill North</t>
-        </is>
+      <c r="M61" t="s">
+        <v>81</v>
       </c>
       <c r="N61">
-        <v>52.89694283226584</v>
+        <v>52.896942832265843</v>
       </c>
       <c r="O61">
-        <v>0.8195439355418687</v>
+        <v>0.81954393554186866</v>
       </c>
       <c r="P61">
         <v>1.737079330946057</v>
       </c>
       <c r="Q61">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R61">
-        <v>2.125500989704398</v>
+        <v>2.1255009897043982</v>
       </c>
       <c r="S61">
-        <v>1.987082749660919</v>
+        <v>1.9870827496609189</v>
       </c>
       <c r="T61">
-        <v>6.926964170543977</v>
+        <v>6.9269641705439771</v>
       </c>
       <c r="U61">
         <v>1.135857329350197</v>
       </c>
       <c r="V61">
-        <v>3.596926814342971</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>3.5969268143429711</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>914</v>
       </c>
@@ -4683,19 +4936,19 @@
         <v>24.26284751</v>
       </c>
       <c r="F62">
-        <v>6.198003328</v>
+        <v>6.1980033280000004</v>
       </c>
       <c r="G62">
         <v>3.2</v>
       </c>
       <c r="H62">
-        <v>793.0648492</v>
+        <v>793.06484920000003</v>
       </c>
       <c r="I62">
-        <v>5.966767372</v>
+        <v>5.9667673719999996</v>
       </c>
       <c r="J62">
-        <v>50.98187311</v>
+        <v>50.981873110000002</v>
       </c>
       <c r="K62">
         <v>7.321131448</v>
@@ -4703,40 +4956,38 @@
       <c r="L62">
         <v>3902</v>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Chapman Mills</t>
-        </is>
+      <c r="M62" t="s">
+        <v>82</v>
       </c>
       <c r="N62">
-        <v>57.52212948074854</v>
+        <v>57.522129480748539</v>
       </c>
       <c r="O62">
-        <v>0.8195439355418687</v>
+        <v>0.81954393554186866</v>
       </c>
       <c r="P62">
-        <v>2.489578945926399</v>
+        <v>2.4895789459263988</v>
       </c>
       <c r="Q62">
         <v>10.24</v>
       </c>
       <c r="R62">
-        <v>2.899308701186719</v>
+        <v>2.8993087011867189</v>
       </c>
       <c r="S62">
-        <v>2.442696741718054</v>
+        <v>2.4426967417180538</v>
       </c>
       <c r="T62">
-        <v>7.140159179598169</v>
+        <v>7.1401591795981689</v>
       </c>
       <c r="U62">
-        <v>0.8645782045079263</v>
+        <v>0.86457820450792633</v>
       </c>
       <c r="V62">
         <v>3.591287265058499</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>915</v>
       </c>
@@ -4759,30 +5010,28 @@
         <v>2.5</v>
       </c>
       <c r="H63">
-        <v>683.4097732</v>
+        <v>683.40977320000002</v>
       </c>
       <c r="I63">
-        <v>4.317460317</v>
+        <v>4.3174603170000001</v>
       </c>
       <c r="J63">
-        <v>37.71428571</v>
+        <v>37.714285709999999</v>
       </c>
       <c r="K63">
-        <v>20.59519784</v>
+        <v>20.595197840000001</v>
       </c>
       <c r="L63">
         <v>2588</v>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Convent Glen - Orléans Woods</t>
-        </is>
+      <c r="M63" t="s">
+        <v>83</v>
       </c>
       <c r="N63">
-        <v>49.16580067485935</v>
+        <v>49.165800674859348</v>
       </c>
       <c r="O63">
-        <v>0.8573324964312685</v>
+        <v>0.85733249643126852</v>
       </c>
       <c r="P63">
         <v>1.287278090779145</v>
@@ -4794,24 +5043,24 @@
         <v>2.83468118519801</v>
       </c>
       <c r="S63">
-        <v>2.077849926486511</v>
+        <v>2.0778499264865111</v>
       </c>
       <c r="T63">
-        <v>6.141195788280976</v>
+        <v>6.1411957882809762</v>
       </c>
       <c r="U63">
         <v>1.313765968198608</v>
       </c>
       <c r="V63">
-        <v>3.412964271996663</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>3.4129642719966631</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>916</v>
       </c>
       <c r="B64">
-        <v>77.25340521</v>
+        <v>77.253405209999997</v>
       </c>
       <c r="C64">
         <v>101728</v>
@@ -4820,10 +5069,10 @@
         <v>4.5</v>
       </c>
       <c r="E64">
-        <v>9.512195122</v>
+        <v>9.5121951219999996</v>
       </c>
       <c r="F64">
-        <v>0.475059382</v>
+        <v>0.47505938199999997</v>
       </c>
       <c r="G64">
         <v>2.8</v>
@@ -4832,42 +5081,40 @@
         <v>10.33103732</v>
       </c>
       <c r="I64">
-        <v>5.357142857</v>
+        <v>5.3571428570000004</v>
       </c>
       <c r="J64">
-        <v>34.15178571</v>
+        <v>34.151785709999999</v>
       </c>
       <c r="K64">
-        <v>16.27078385</v>
+        <v>16.270783850000001</v>
       </c>
       <c r="L64">
         <v>4057</v>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Cumberland</t>
-        </is>
+      <c r="M64" t="s">
+        <v>84</v>
       </c>
       <c r="N64">
-        <v>8.789391629117455</v>
+        <v>8.7893916291174552</v>
       </c>
       <c r="O64">
-        <v>0.6532125137753437</v>
+        <v>0.65321251377534373</v>
       </c>
       <c r="P64">
-        <v>0.6892455164888633</v>
+        <v>0.68924551648886334</v>
       </c>
       <c r="Q64">
         <v>7.839999999999999</v>
       </c>
       <c r="R64">
-        <v>1.014143930399985</v>
+        <v>1.0141439303999851</v>
       </c>
       <c r="S64">
-        <v>2.314550249400518</v>
+        <v>2.3145502494005181</v>
       </c>
       <c r="T64">
-        <v>5.843952918188167</v>
+        <v>5.8439529181881671</v>
       </c>
       <c r="U64">
         <v>1.211408475710648</v>
@@ -4876,12 +5123,12 @@
         <v>3.608205007704326</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>917</v>
       </c>
       <c r="B65">
-        <v>135.4044813</v>
+        <v>135.40448129999999</v>
       </c>
       <c r="C65">
         <v>65685</v>
@@ -4893,7 +5140,7 @@
         <v>26.21359223</v>
       </c>
       <c r="F65">
-        <v>4.249291785</v>
+        <v>4.2492917849999996</v>
       </c>
       <c r="G65">
         <v>1.7</v>
@@ -4905,18 +5152,16 @@
         <v>12.94964029</v>
       </c>
       <c r="J65">
-        <v>41.00719424</v>
+        <v>41.007194239999997</v>
       </c>
       <c r="K65">
-        <v>50.7082153</v>
+        <v>50.708215299999999</v>
       </c>
       <c r="L65">
         <v>3693</v>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>East Industrial</t>
-        </is>
+      <c r="M65" t="s">
+        <v>85</v>
       </c>
       <c r="N65">
         <v>11.63634312402311</v>
@@ -4925,7 +5170,7 @@
         <v>1.060697840353612</v>
       </c>
       <c r="P65">
-        <v>2.061381038284771</v>
+        <v>2.0613810382847708</v>
       </c>
       <c r="Q65">
         <v>2.89</v>
@@ -4934,24 +5179,24 @@
         <v>3.473406532153708</v>
       </c>
       <c r="S65">
-        <v>3.598560863734279</v>
+        <v>3.5985608637342792</v>
       </c>
       <c r="T65">
-        <v>6.40368598855378</v>
+        <v>6.4036859885537796</v>
       </c>
       <c r="U65">
         <v>1.705078325613907</v>
       </c>
       <c r="V65">
-        <v>3.567379307650979</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>3.5673793076509792</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>918</v>
       </c>
       <c r="B66">
-        <v>21.31637476</v>
+        <v>21.316374759999999</v>
       </c>
       <c r="C66">
         <v>72694</v>
@@ -4963,13 +5208,13 @@
         <v>3.539823009</v>
       </c>
       <c r="F66">
-        <v>0.281293952</v>
+        <v>0.28129395200000001</v>
       </c>
       <c r="G66">
         <v>2.5</v>
       </c>
       <c r="H66">
-        <v>17.274958</v>
+        <v>17.274958000000002</v>
       </c>
       <c r="I66">
         <v>12.38095238</v>
@@ -4983,45 +5228,43 @@
       <c r="L66">
         <v>3818</v>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Edwards - Carlsbad Springs</t>
-        </is>
+      <c r="M66" t="s">
+        <v>86</v>
       </c>
       <c r="N66">
-        <v>4.616965969118681</v>
+        <v>4.6169659691186808</v>
       </c>
       <c r="O66">
-        <v>0.8808135922807914</v>
+        <v>0.88081359228079137</v>
       </c>
       <c r="P66">
-        <v>0.5303715226141011</v>
+        <v>0.53037152261410114</v>
       </c>
       <c r="Q66">
         <v>6.25</v>
       </c>
       <c r="R66">
-        <v>1.237417000162565</v>
+        <v>1.2374170001625651</v>
       </c>
       <c r="S66">
-        <v>3.518657752609651</v>
+        <v>3.5186577526096512</v>
       </c>
       <c r="T66">
-        <v>3.58568582840159</v>
+        <v>3.5856858284015898</v>
       </c>
       <c r="U66">
-        <v>1.185556897102881</v>
+        <v>1.1855568971028809</v>
       </c>
       <c r="V66">
-        <v>3.581835924057648</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>3.5818359240576481</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>919</v>
       </c>
       <c r="B67">
-        <v>2906.199797</v>
+        <v>2906.1997970000002</v>
       </c>
       <c r="C67">
         <v>67643</v>
@@ -5030,68 +5273,66 @@
         <v>8.1</v>
       </c>
       <c r="E67">
-        <v>20.8566108</v>
+        <v>20.856610799999999</v>
       </c>
       <c r="F67">
-        <v>3.180060163</v>
+        <v>3.1800601629999998</v>
       </c>
       <c r="G67">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H67">
-        <v>710.6264222999999</v>
+        <v>710.62642229999994</v>
       </c>
       <c r="I67">
         <v>6.377952756</v>
       </c>
       <c r="J67">
-        <v>45.7480315</v>
+        <v>45.748031500000003</v>
       </c>
       <c r="K67">
-        <v>18.60764933</v>
+        <v>18.607649330000001</v>
       </c>
       <c r="L67">
         <v>3890</v>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Elmvale - Canterbury</t>
-        </is>
+      <c r="M67" t="s">
+        <v>87</v>
       </c>
       <c r="N67">
-        <v>53.90918100843307</v>
+        <v>53.909181008433073</v>
       </c>
       <c r="O67">
-        <v>0.9084850188786497</v>
+        <v>0.90848501887864974</v>
       </c>
       <c r="P67">
         <v>1.783272318800468</v>
       </c>
       <c r="Q67">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R67">
         <v>2.851641351261605</v>
       </c>
       <c r="S67">
-        <v>2.525460899717119</v>
+        <v>2.5254608997171188</v>
       </c>
       <c r="T67">
-        <v>6.763729111961833</v>
+        <v>6.7637291119618332</v>
       </c>
       <c r="U67">
         <v>1.269691512975464</v>
       </c>
       <c r="V67">
-        <v>3.589949601325708</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>3.5899496013257082</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>920</v>
       </c>
       <c r="B68">
-        <v>3295.706221</v>
+        <v>3295.7062209999999</v>
       </c>
       <c r="C68">
         <v>95208</v>
@@ -5109,13 +5350,13 @@
         <v>2.9</v>
       </c>
       <c r="H68">
-        <v>507.6790008</v>
+        <v>507.67900079999998</v>
       </c>
       <c r="I68">
-        <v>3.864278982</v>
+        <v>3.8642789820000001</v>
       </c>
       <c r="J68">
-        <v>38.3600377</v>
+        <v>38.360037699999999</v>
       </c>
       <c r="K68">
         <v>11.0106383</v>
@@ -5123,16 +5364,14 @@
       <c r="L68">
         <v>3611</v>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Fallingbrook</t>
-        </is>
+      <c r="M68" t="s">
+        <v>88</v>
       </c>
       <c r="N68">
-        <v>57.4082417515116</v>
+        <v>57.408241751511603</v>
       </c>
       <c r="O68">
-        <v>0.7558748556724915</v>
+        <v>0.75587485567249146</v>
       </c>
       <c r="P68">
         <v>1.187097165778775</v>
@@ -5141,22 +5380,22 @@
         <v>8.41</v>
       </c>
       <c r="R68">
-        <v>2.705589199990592</v>
+        <v>2.7055891999905919</v>
       </c>
       <c r="S68">
         <v>1.965776941059183</v>
       </c>
       <c r="T68">
-        <v>6.193548070371295</v>
+        <v>6.1935480703712953</v>
       </c>
       <c r="U68">
         <v>1.04181249627716</v>
       </c>
       <c r="V68">
-        <v>3.557627488426827</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>3.5576274884268271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>921</v>
       </c>
@@ -5179,59 +5418,57 @@
         <v>3.3</v>
       </c>
       <c r="H69">
-        <v>273.8455289</v>
+        <v>273.84552889999998</v>
       </c>
       <c r="I69">
-        <v>5.5613851</v>
+        <v>5.5613850999999999</v>
       </c>
       <c r="J69">
         <v>47.11437566</v>
       </c>
       <c r="K69">
-        <v>5.724098454</v>
+        <v>5.7240984539999999</v>
       </c>
       <c r="L69">
         <v>6324</v>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Findlay Creek</t>
-        </is>
+      <c r="M69" t="s">
+        <v>89</v>
       </c>
       <c r="N69">
-        <v>29.97082505871335</v>
+        <v>29.970825058713348</v>
       </c>
       <c r="O69">
-        <v>0.8195439355418687</v>
+        <v>0.81954393554186866</v>
       </c>
       <c r="P69">
-        <v>2.071973417059205</v>
+        <v>2.0719734170592048</v>
       </c>
       <c r="Q69">
         <v>10.89</v>
       </c>
       <c r="R69">
-        <v>2.437505654558542</v>
+        <v>2.4375056545585418</v>
       </c>
       <c r="S69">
-        <v>2.358258912842269</v>
+        <v>2.3582589128422691</v>
       </c>
       <c r="T69">
-        <v>6.863991233968761</v>
+        <v>6.8639912339687612</v>
       </c>
       <c r="U69">
-        <v>0.7577070949796328</v>
+        <v>0.75770709497963284</v>
       </c>
       <c r="V69">
         <v>3.800991861260171</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>922</v>
       </c>
       <c r="B70">
-        <v>23.89053657</v>
+        <v>23.890536569999998</v>
       </c>
       <c r="C70">
         <v>77268</v>
@@ -5240,7 +5477,7 @@
         <v>4</v>
       </c>
       <c r="E70">
-        <v>0.955414013</v>
+        <v>0.95541401299999995</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -5252,21 +5489,19 @@
         <v>1.878698542</v>
       </c>
       <c r="I70">
-        <v>6.35359116</v>
+        <v>6.3535911599999997</v>
       </c>
       <c r="J70">
-        <v>22.09944751</v>
+        <v>22.099447510000001</v>
       </c>
       <c r="K70">
-        <v>20.74303406</v>
+        <v>20.743034059999999</v>
       </c>
       <c r="L70">
         <v>1905</v>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Fitzroy</t>
-        </is>
+      <c r="M70" t="s">
+        <v>90</v>
       </c>
       <c r="N70">
         <v>4.887794653010701</v>
@@ -5284,7 +5519,7 @@
         <v>0.2738570983286947</v>
       </c>
       <c r="S70">
-        <v>2.52063308714299</v>
+        <v>2.5206330871429898</v>
       </c>
       <c r="T70">
         <v>4.701004946817223</v>
@@ -5293,15 +5528,15 @@
         <v>1.316872280459175</v>
       </c>
       <c r="V70">
-        <v>3.279894980011638</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>3.2798949800116382</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>923</v>
       </c>
       <c r="B71">
-        <v>4650.890038</v>
+        <v>4650.8900379999995</v>
       </c>
       <c r="C71">
         <v>79146</v>
@@ -5310,63 +5545,61 @@
         <v>6.2</v>
       </c>
       <c r="E71">
-        <v>16.38954869</v>
+        <v>16.389548690000002</v>
       </c>
       <c r="F71">
-        <v>2.485207101</v>
+        <v>2.4852071009999999</v>
       </c>
       <c r="G71">
         <v>2.1</v>
       </c>
       <c r="H71">
-        <v>2889.97317</v>
+        <v>2889.9731700000002</v>
       </c>
       <c r="I71">
-        <v>2.279202279</v>
+        <v>2.2792022790000002</v>
       </c>
       <c r="J71">
-        <v>72.15099714999999</v>
+        <v>72.150997149999995</v>
       </c>
       <c r="K71">
-        <v>16.13412229</v>
+        <v>16.134122290000001</v>
       </c>
       <c r="L71">
         <v>3259</v>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Glebe - Dows Lake</t>
-        </is>
+      <c r="M71" t="s">
+        <v>91</v>
       </c>
       <c r="N71">
-        <v>68.1974342479246</v>
+        <v>68.197434247924605</v>
       </c>
       <c r="O71">
-        <v>0.7923916894982539</v>
+        <v>0.79239168949825389</v>
       </c>
       <c r="P71">
-        <v>1.576453964123279</v>
+        <v>1.5764539641232791</v>
       </c>
       <c r="Q71">
         <v>4.41</v>
       </c>
       <c r="R71">
-        <v>3.460893810862071</v>
+        <v>3.4608938108620708</v>
       </c>
       <c r="S71">
-        <v>1.509702712125801</v>
+        <v>1.5097027121258011</v>
       </c>
       <c r="T71">
-        <v>8.49417430654681</v>
+        <v>8.4941743065468103</v>
       </c>
       <c r="U71">
         <v>1.207745344392672</v>
       </c>
       <c r="V71">
-        <v>3.513084360465144</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>3.5130843604651441</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>924</v>
       </c>
@@ -5403,22 +5636,20 @@
       <c r="L72">
         <v>3244</v>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Glen Cairn - Kanata South Business Park</t>
-        </is>
+      <c r="M72" t="s">
+        <v>92</v>
       </c>
       <c r="N72">
-        <v>49.47162527146243</v>
+        <v>49.471625271462429</v>
       </c>
       <c r="O72">
-        <v>0.8061799739838872</v>
+        <v>0.80617997398388719</v>
       </c>
       <c r="P72">
         <v>1.560328743887005</v>
       </c>
       <c r="Q72">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R72">
         <v>3.031755430329552</v>
@@ -5430,18 +5661,18 @@
         <v>5.288548950326545</v>
       </c>
       <c r="U72">
-        <v>1.101196489440048</v>
+        <v>1.1011964894400481</v>
       </c>
       <c r="V72">
         <v>3.511080845539118</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>925</v>
       </c>
       <c r="B73">
-        <v>141.5604833</v>
+        <v>141.56048329999999</v>
       </c>
       <c r="C73">
         <v>109395</v>
@@ -5450,42 +5681,40 @@
         <v>5</v>
       </c>
       <c r="E73">
-        <v>4.471544715</v>
+        <v>4.4715447150000003</v>
       </c>
       <c r="F73">
-        <v>0.609756098</v>
+        <v>0.60975609799999997</v>
       </c>
       <c r="G73">
         <v>2.9</v>
       </c>
       <c r="H73">
-        <v>37.43296521</v>
+        <v>37.432965209999999</v>
       </c>
       <c r="I73">
-        <v>5.662100457</v>
+        <v>5.6621004570000002</v>
       </c>
       <c r="J73">
-        <v>36.62100457</v>
+        <v>36.621004569999997</v>
       </c>
       <c r="K73">
-        <v>11.58536585</v>
+        <v>11.585365850000001</v>
       </c>
       <c r="L73">
         <v>3449</v>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Greely</t>
-        </is>
+      <c r="M73" t="s">
+        <v>93</v>
       </c>
       <c r="N73">
-        <v>11.89791928447995</v>
+        <v>11.897919284479951</v>
       </c>
       <c r="O73">
-        <v>0.6989700043360189</v>
+        <v>0.69897000433601886</v>
       </c>
       <c r="P73">
-        <v>0.7808688097241431</v>
+        <v>0.78086880972414308</v>
       </c>
       <c r="Q73">
         <v>8.41</v>
@@ -5497,21 +5726,21 @@
         <v>2.379516853691102</v>
       </c>
       <c r="T73">
-        <v>6.051529110067967</v>
+        <v>6.0515291100679667</v>
       </c>
       <c r="U73">
-        <v>1.063909752767985</v>
+        <v>1.0639097527679851</v>
       </c>
       <c r="V73">
         <v>3.537693194367391</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>927</v>
       </c>
       <c r="B74">
-        <v>1174.566749</v>
+        <v>1174.5667490000001</v>
       </c>
       <c r="C74">
         <v>91159</v>
@@ -5520,54 +5749,52 @@
         <v>6.3</v>
       </c>
       <c r="E74">
-        <v>18.77470356</v>
+        <v>18.774703559999999</v>
       </c>
       <c r="F74">
-        <v>1.90397351</v>
+        <v>1.9039735099999999</v>
       </c>
       <c r="G74">
         <v>2.4</v>
       </c>
       <c r="H74">
-        <v>261.1660834</v>
+        <v>261.16608339999999</v>
       </c>
       <c r="I74">
-        <v>4.753820034</v>
+        <v>4.7538200340000003</v>
       </c>
       <c r="J74">
-        <v>55.68760611</v>
+        <v>55.687606109999997</v>
       </c>
       <c r="K74">
-        <v>27.56622517</v>
+        <v>27.566225169999999</v>
       </c>
       <c r="L74">
         <v>3383</v>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Hunt Club Woods - Quintarra - Revelstoke</t>
-        </is>
+      <c r="M74" t="s">
+        <v>94</v>
       </c>
       <c r="N74">
-        <v>34.27195280400579</v>
+        <v>34.271952804005792</v>
       </c>
       <c r="O74">
-        <v>0.7993405494535817</v>
+        <v>0.79934054945358168</v>
       </c>
       <c r="P74">
-        <v>1.379845465985231</v>
+        <v>1.3798454659852311</v>
       </c>
       <c r="Q74">
         <v>5.76</v>
       </c>
       <c r="R74">
-        <v>2.416916776168759</v>
+        <v>2.4169167761687591</v>
       </c>
       <c r="S74">
-        <v>2.180325671545423</v>
+        <v>2.1803256715454231</v>
       </c>
       <c r="T74">
-        <v>7.462412887933768</v>
+        <v>7.4624128879337679</v>
       </c>
       <c r="U74">
         <v>1.440377299291111</v>
@@ -5576,7 +5803,7 @@
         <v>3.52930199778798</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>928</v>
       </c>
@@ -5590,7 +5817,7 @@
         <v>6.1</v>
       </c>
       <c r="E75">
-        <v>16.53116531</v>
+        <v>16.531165309999999</v>
       </c>
       <c r="F75">
         <v>4.338592233</v>
@@ -5605,7 +5832,7 @@
         <v>1.676646707</v>
       </c>
       <c r="J75">
-        <v>67.78443114</v>
+        <v>67.784431139999995</v>
       </c>
       <c r="K75">
         <v>16.90440061</v>
@@ -5613,45 +5840,43 @@
       <c r="L75">
         <v>1677</v>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Kanata Lakes - Arcadia</t>
-        </is>
+      <c r="M75" t="s">
+        <v>95</v>
       </c>
       <c r="N75">
-        <v>37.08065382379334</v>
+        <v>37.080653823793341</v>
       </c>
       <c r="O75">
-        <v>0.785329835010767</v>
+        <v>0.78532983501076703</v>
       </c>
       <c r="P75">
-        <v>2.082928763304209</v>
+        <v>2.0829287633042091</v>
       </c>
       <c r="Q75">
         <v>7.839999999999999</v>
       </c>
       <c r="R75">
-        <v>2.655228178930462</v>
+        <v>2.6552281789304621</v>
       </c>
       <c r="S75">
         <v>1.294853932688935</v>
       </c>
       <c r="T75">
-        <v>8.233130093712839</v>
+        <v>8.2331300937128393</v>
       </c>
       <c r="U75">
-        <v>1.227999776321281</v>
+        <v>1.2279997763212811</v>
       </c>
       <c r="V75">
-        <v>3.224533062606086</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>3.2245330626060862</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>929</v>
       </c>
       <c r="B76">
-        <v>2060.508819</v>
+        <v>2060.5088190000001</v>
       </c>
       <c r="C76">
         <v>82250</v>
@@ -5663,7 +5888,7 @@
         <v>20.28343667</v>
       </c>
       <c r="F76">
-        <v>2.022867194</v>
+        <v>2.0228671939999998</v>
       </c>
       <c r="G76">
         <v>2.6</v>
@@ -5683,45 +5908,43 @@
       <c r="L76">
         <v>2923</v>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Katimavik - Hazeldean</t>
-        </is>
+      <c r="M76" t="s">
+        <v>96</v>
       </c>
       <c r="N76">
         <v>45.39282783656467</v>
       </c>
       <c r="O76">
-        <v>0.8750612633917001</v>
+        <v>0.87506126339170009</v>
       </c>
       <c r="P76">
-        <v>1.42227535800913</v>
+        <v>1.4222753580091301</v>
       </c>
       <c r="Q76">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R76">
-        <v>3.097126040579303</v>
+        <v>3.0971260405793029</v>
       </c>
       <c r="S76">
-        <v>2.23606797749979</v>
+        <v>2.2360679774997898</v>
       </c>
       <c r="T76">
-        <v>6.31238099689808</v>
+        <v>6.3123809968980797</v>
       </c>
       <c r="U76">
-        <v>1.137364133581538</v>
+        <v>1.1373641335815381</v>
       </c>
       <c r="V76">
-        <v>3.465828815357436</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>3.4658288153574359</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>931</v>
       </c>
       <c r="B77">
-        <v>3541.955891</v>
+        <v>3541.9558910000001</v>
       </c>
       <c r="C77">
         <v>73629</v>
@@ -5730,68 +5953,66 @@
         <v>6.9</v>
       </c>
       <c r="E77">
-        <v>22.28637413</v>
+        <v>22.286374129999999</v>
       </c>
       <c r="F77">
-        <v>2.582644628</v>
+        <v>2.5826446280000002</v>
       </c>
       <c r="G77">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H77">
-        <v>1474.229369</v>
+        <v>1474.2293689999999</v>
       </c>
       <c r="I77">
-        <v>3.803803804</v>
+        <v>3.8038038040000002</v>
       </c>
       <c r="J77">
-        <v>65.56556557</v>
+        <v>65.565565570000004</v>
       </c>
       <c r="K77">
-        <v>21.17768595</v>
+        <v>21.177685950000001</v>
       </c>
       <c r="L77">
         <v>2219</v>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Laurentian</t>
-        </is>
+      <c r="M77" t="s">
+        <v>97</v>
       </c>
       <c r="N77">
-        <v>59.51433349202527</v>
+        <v>59.514333492025273</v>
       </c>
       <c r="O77">
-        <v>0.8388490907372553</v>
+        <v>0.83884909073725533</v>
       </c>
       <c r="P77">
         <v>1.607060866302207</v>
       </c>
       <c r="Q77">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R77">
         <v>3.168565058788559</v>
       </c>
       <c r="S77">
-        <v>1.950334280065856</v>
+        <v>1.9503342800658561</v>
       </c>
       <c r="T77">
         <v>8.097256669391184</v>
       </c>
       <c r="U77">
-        <v>1.325878503738887</v>
+        <v>1.3258785037388869</v>
       </c>
       <c r="V77">
-        <v>3.346157302232008</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>3.3461573022320081</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>932</v>
       </c>
       <c r="B78">
-        <v>5026.13944</v>
+        <v>5026.1394399999999</v>
       </c>
       <c r="C78">
         <v>40155</v>
@@ -5800,7 +6021,7 @@
         <v>14.5</v>
       </c>
       <c r="E78">
-        <v>33.26693227</v>
+        <v>33.266932269999998</v>
       </c>
       <c r="F78">
         <v>12.42120875</v>
@@ -5809,7 +6030,7 @@
         <v>2.6</v>
       </c>
       <c r="H78">
-        <v>985.100967</v>
+        <v>985.10096699999997</v>
       </c>
       <c r="I78">
         <v>20.11453114</v>
@@ -5818,50 +6039,48 @@
         <v>25.62634216</v>
       </c>
       <c r="K78">
-        <v>8.935854653</v>
+        <v>8.9358546529999998</v>
       </c>
       <c r="L78">
         <v>7915</v>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Ledbury - Heron Gate - Ridgemont</t>
-        </is>
+      <c r="M78" t="s">
+        <v>98</v>
       </c>
       <c r="N78">
-        <v>70.89527092832074</v>
+        <v>70.895270928320741</v>
       </c>
       <c r="O78">
         <v>1.161368002234975</v>
       </c>
       <c r="P78">
-        <v>3.524373525890807</v>
+        <v>3.5243735258908071</v>
       </c>
       <c r="Q78">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R78">
-        <v>2.993480745384643</v>
+        <v>2.9934807453846428</v>
       </c>
       <c r="S78">
         <v>4.484922645932703</v>
       </c>
       <c r="T78">
-        <v>5.062246750208844</v>
+        <v>5.0622467502088444</v>
       </c>
       <c r="U78">
-        <v>0.9511360961064975</v>
+        <v>0.95113609610649752</v>
       </c>
       <c r="V78">
-        <v>3.898450919198375</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>3.8984509191983752</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>933</v>
       </c>
       <c r="B79">
-        <v>2887.435929</v>
+        <v>2887.4359290000002</v>
       </c>
       <c r="C79">
         <v>82374</v>
@@ -5870,7 +6089,7 @@
         <v>4</v>
       </c>
       <c r="E79">
-        <v>20.12448133</v>
+        <v>20.124481329999998</v>
       </c>
       <c r="F79">
         <v>2.242609582</v>
@@ -5882,10 +6101,10 @@
         <v>680.9879439</v>
       </c>
       <c r="I79">
-        <v>2.056074766</v>
+        <v>2.0560747660000001</v>
       </c>
       <c r="J79">
-        <v>74.39252336</v>
+        <v>74.392523359999998</v>
       </c>
       <c r="K79">
         <v>22.30142566</v>
@@ -5893,10 +6112,8 @@
       <c r="L79">
         <v>2592</v>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Lindenlea - New Edinburgh</t>
-        </is>
+      <c r="M79" t="s">
+        <v>99</v>
       </c>
       <c r="N79">
         <v>53.73486697666609</v>
@@ -5911,27 +6128,27 @@
         <v>4</v>
       </c>
       <c r="R79">
-        <v>2.833139423301844</v>
+        <v>2.8331394233018439</v>
       </c>
       <c r="S79">
-        <v>1.433901937372288</v>
+        <v>1.4339019373722881</v>
       </c>
       <c r="T79">
-        <v>8.625110049152996</v>
+        <v>8.6251100491529957</v>
       </c>
       <c r="U79">
-        <v>1.348332627015887</v>
+        <v>1.3483326270158871</v>
       </c>
       <c r="V79">
-        <v>3.413634997198556</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>3.4136349971985558</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>934</v>
       </c>
       <c r="B80">
-        <v>7826.832299</v>
+        <v>7826.8322989999997</v>
       </c>
       <c r="C80">
         <v>34677</v>
@@ -5940,42 +6157,40 @@
         <v>13.7</v>
       </c>
       <c r="E80">
-        <v>32.43243243</v>
+        <v>32.432432429999999</v>
       </c>
       <c r="F80">
-        <v>3.706688155</v>
+        <v>3.7066881550000002</v>
       </c>
       <c r="G80">
         <v>1.8</v>
       </c>
       <c r="H80">
-        <v>4400.937611</v>
+        <v>4400.9376110000003</v>
       </c>
       <c r="I80">
         <v>11.634757</v>
       </c>
       <c r="J80">
-        <v>38.88070692</v>
+        <v>38.880706920000002</v>
       </c>
       <c r="K80">
-        <v>17.48589847</v>
+        <v>17.485898469999999</v>
       </c>
       <c r="L80">
         <v>6031</v>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Lowertown</t>
-        </is>
+      <c r="M80" t="s">
+        <v>100</v>
       </c>
       <c r="N80">
-        <v>88.46938622484051</v>
+        <v>88.469386224840505</v>
       </c>
       <c r="O80">
-        <v>1.136720567156407</v>
+        <v>1.1367205671564069</v>
       </c>
       <c r="P80">
-        <v>1.925276124352037</v>
+        <v>1.9252761243520371</v>
       </c>
       <c r="Q80">
         <v>3.24</v>
@@ -5984,19 +6199,19 @@
         <v>3.64354521191889</v>
       </c>
       <c r="S80">
-        <v>3.410975960044281</v>
+        <v>3.4109759600442811</v>
       </c>
       <c r="T80">
-        <v>6.235439593164222</v>
+        <v>6.2354395931642221</v>
       </c>
       <c r="U80">
         <v>1.242687952375217</v>
       </c>
       <c r="V80">
-        <v>3.780389328470953</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>3.7803893284709531</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>935</v>
       </c>
@@ -6007,19 +6222,19 @@
         <v>52838</v>
       </c>
       <c r="D81">
-        <v>8.300000000000001</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E81">
-        <v>30.05093379</v>
+        <v>30.050933789999998</v>
       </c>
       <c r="F81">
-        <v>6.142857143</v>
+        <v>6.1428571429999996</v>
       </c>
       <c r="G81">
         <v>1.9</v>
       </c>
       <c r="H81">
-        <v>557.2256818</v>
+        <v>557.22568179999996</v>
       </c>
       <c r="I81">
         <v>10.42216359</v>
@@ -6028,21 +6243,19 @@
         <v>44.85488127</v>
       </c>
       <c r="K81">
-        <v>23.37383846</v>
+        <v>23.373838460000002</v>
       </c>
       <c r="L81">
         <v>3456</v>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Manor Park</t>
-        </is>
+      <c r="M81" t="s">
+        <v>101</v>
       </c>
       <c r="N81">
-        <v>60.67948582511226</v>
+        <v>60.679485825112259</v>
       </c>
       <c r="O81">
-        <v>0.919078092376074</v>
+        <v>0.91907809237607396</v>
       </c>
       <c r="P81">
         <v>2.47847879615703</v>
@@ -6054,19 +6267,19 @@
         <v>2.746031124275611</v>
       </c>
       <c r="S81">
-        <v>3.228337589224522</v>
+        <v>3.2283375892245219</v>
       </c>
       <c r="T81">
-        <v>6.697378686471297</v>
+        <v>6.6973786864712972</v>
       </c>
       <c r="U81">
         <v>1.368730038242036</v>
       </c>
       <c r="V81">
-        <v>3.538573733806856</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>3.5385737338068561</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>936</v>
       </c>
@@ -6080,7 +6293,7 @@
         <v>3.8</v>
       </c>
       <c r="E82">
-        <v>7.397959184</v>
+        <v>7.3979591840000003</v>
       </c>
       <c r="F82">
         <v>0.362318841</v>
@@ -6089,13 +6302,13 @@
         <v>2.7</v>
       </c>
       <c r="H82">
-        <v>9.993779533</v>
+        <v>9.9937795329999997</v>
       </c>
       <c r="I82">
-        <v>8.176100629</v>
+        <v>8.1761006290000005</v>
       </c>
       <c r="J82">
-        <v>25.99580713</v>
+        <v>25.995807129999999</v>
       </c>
       <c r="K82">
         <v>15.68154403</v>
@@ -6103,31 +6316,29 @@
       <c r="L82">
         <v>3782</v>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Navan - Sarsfield</t>
-        </is>
+      <c r="M82" t="s">
+        <v>102</v>
       </c>
       <c r="N82">
         <v>6.106187280947089</v>
       </c>
       <c r="O82">
-        <v>0.5797835966168101</v>
+        <v>0.57978359661681012</v>
       </c>
       <c r="P82">
-        <v>0.601929265777965</v>
+        <v>0.60192926577796502</v>
       </c>
       <c r="Q82">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R82">
-        <v>0.9997297644924346</v>
+        <v>0.99972976449243456</v>
       </c>
       <c r="S82">
         <v>2.859388156406891</v>
       </c>
       <c r="T82">
-        <v>5.098608352285945</v>
+        <v>5.0986083522859449</v>
       </c>
       <c r="U82">
         <v>1.195388821785627</v>
@@ -6136,12 +6347,12 @@
         <v>3.577721524509021</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>937</v>
       </c>
       <c r="B83">
-        <v>4103.690054</v>
+        <v>4103.6900539999997</v>
       </c>
       <c r="C83">
         <v>88476</v>
@@ -6150,68 +6361,66 @@
         <v>6</v>
       </c>
       <c r="E83">
-        <v>21.65775401</v>
+        <v>21.657754010000001</v>
       </c>
       <c r="F83">
-        <v>3.322127744</v>
+        <v>3.3221277439999999</v>
       </c>
       <c r="G83">
         <v>3</v>
       </c>
       <c r="H83">
-        <v>392.7597362</v>
+        <v>392.75973620000002</v>
       </c>
       <c r="I83">
-        <v>4.556693748</v>
+        <v>4.5566937479999998</v>
       </c>
       <c r="J83">
-        <v>41.43412222</v>
+        <v>41.434122219999999</v>
       </c>
       <c r="K83">
-        <v>7.395689144</v>
+        <v>7.3956891440000003</v>
       </c>
       <c r="L83">
         <v>4199</v>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Old Barrhaven East</t>
-        </is>
+      <c r="M83" t="s">
+        <v>103</v>
       </c>
       <c r="N83">
-        <v>64.06005037462896</v>
+        <v>64.060050374628958</v>
       </c>
       <c r="O83">
-        <v>0.7781512503836436</v>
+        <v>0.77815125038364363</v>
       </c>
       <c r="P83">
-        <v>1.822670497923308</v>
+        <v>1.8226704979233079</v>
       </c>
       <c r="Q83">
         <v>9</v>
       </c>
       <c r="R83">
-        <v>2.594126959658606</v>
+        <v>2.5941269596586061</v>
       </c>
       <c r="S83">
-        <v>2.134641362852318</v>
+        <v>2.1346413628523182</v>
       </c>
       <c r="T83">
-        <v>6.436934225234867</v>
+        <v>6.4369342252348671</v>
       </c>
       <c r="U83">
-        <v>0.8689786485819632</v>
+        <v>0.86897864858196316</v>
       </c>
       <c r="V83">
         <v>3.623145874637939</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>938</v>
       </c>
       <c r="B84">
-        <v>3522.933804</v>
+        <v>3522.9338039999998</v>
       </c>
       <c r="C84">
         <v>91119</v>
@@ -6220,7 +6429,7 @@
         <v>6.1</v>
       </c>
       <c r="E84">
-        <v>17.96407186</v>
+        <v>17.964071860000001</v>
       </c>
       <c r="F84">
         <v>1.502086231</v>
@@ -6232,10 +6441,10 @@
         <v>421.5761119</v>
       </c>
       <c r="I84">
-        <v>3.870651641</v>
+        <v>3.8706516409999998</v>
       </c>
       <c r="J84">
-        <v>40.07839294</v>
+        <v>40.078392940000001</v>
       </c>
       <c r="K84">
         <v>11.48817803</v>
@@ -6243,16 +6452,14 @@
       <c r="L84">
         <v>2994</v>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Old Barrhaven West</t>
-        </is>
+      <c r="M84" t="s">
+        <v>104</v>
       </c>
       <c r="N84">
-        <v>59.35430737528659</v>
+        <v>59.354307375286588</v>
       </c>
       <c r="O84">
-        <v>0.785329835010767</v>
+        <v>0.78532983501076703</v>
       </c>
       <c r="P84">
         <v>1.225596275696039</v>
@@ -6261,27 +6468,27 @@
         <v>7.839999999999999</v>
       </c>
       <c r="R84">
-        <v>2.624875994130638</v>
+        <v>2.6248759941306381</v>
       </c>
       <c r="S84">
         <v>1.967397174187256</v>
       </c>
       <c r="T84">
-        <v>6.330749792876039</v>
+        <v>6.3307497928760386</v>
       </c>
       <c r="U84">
-        <v>1.060251157125203</v>
+        <v>1.0602511571252029</v>
       </c>
       <c r="V84">
         <v>3.476251796007034</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>939</v>
       </c>
       <c r="B85">
-        <v>3173.168645</v>
+        <v>3173.1686450000002</v>
       </c>
       <c r="C85">
         <v>91279</v>
@@ -6293,7 +6500,7 @@
         <v>22.43083004</v>
       </c>
       <c r="F85">
-        <v>1.880424301</v>
+        <v>1.8804243009999999</v>
       </c>
       <c r="G85">
         <v>2.7</v>
@@ -6302,42 +6509,40 @@
         <v>468.1724231</v>
       </c>
       <c r="I85">
-        <v>5.877192982</v>
+        <v>5.8771929820000004</v>
       </c>
       <c r="J85">
-        <v>37.71929825</v>
+        <v>37.719298250000001</v>
       </c>
       <c r="K85">
-        <v>15.67020251</v>
+        <v>15.670202509999999</v>
       </c>
       <c r="L85">
         <v>3384</v>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Orléans Village - Chateauneuf</t>
-        </is>
+      <c r="M85" t="s">
+        <v>105</v>
       </c>
       <c r="N85">
-        <v>56.33088535608152</v>
+        <v>56.330885356081517</v>
       </c>
       <c r="O85">
-        <v>0.785329835010767</v>
+        <v>0.78532983501076703</v>
       </c>
       <c r="P85">
         <v>1.371285638005445</v>
       </c>
       <c r="Q85">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R85">
-        <v>2.670405828736473</v>
+        <v>2.6704058287364729</v>
       </c>
       <c r="S85">
-        <v>2.424292264146384</v>
+        <v>2.4242922641463842</v>
       </c>
       <c r="T85">
-        <v>6.141603882537525</v>
+        <v>6.1416038825375248</v>
       </c>
       <c r="U85">
         <v>1.195074609002555</v>
@@ -6346,7 +6551,7 @@
         <v>3.529430354366986</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>940</v>
       </c>
@@ -6360,19 +6565,19 @@
         <v>11.6</v>
       </c>
       <c r="E86">
-        <v>29.08638906</v>
+        <v>29.086389059999998</v>
       </c>
       <c r="F86">
-        <v>8.537859008</v>
+        <v>8.5378590079999999</v>
       </c>
       <c r="G86">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H86">
-        <v>2397.161254</v>
+        <v>2397.1612540000001</v>
       </c>
       <c r="I86">
-        <v>16.71361502</v>
+        <v>16.713615019999999</v>
       </c>
       <c r="J86">
         <v>29.01408451</v>
@@ -6383,22 +6588,20 @@
       <c r="L86">
         <v>5792</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Overbrook - McArthur</t>
-        </is>
+      <c r="M86" t="s">
+        <v>106</v>
       </c>
       <c r="N86">
-        <v>56.03499371821148</v>
+        <v>56.034993718211481</v>
       </c>
       <c r="O86">
-        <v>1.064457989226918</v>
+        <v>1.0644579892269179</v>
       </c>
       <c r="P86">
-        <v>2.921961500088596</v>
+        <v>2.9219615000885959</v>
       </c>
       <c r="Q86">
-        <v>4.840000000000001</v>
+        <v>4.8400000000000007</v>
       </c>
       <c r="R86">
         <v>3.37969724945579</v>
@@ -6407,16 +6610,16 @@
         <v>4.088228836550126</v>
       </c>
       <c r="T86">
-        <v>5.386472362316547</v>
+        <v>5.3864723623165469</v>
       </c>
       <c r="U86">
         <v>1.164989252987944</v>
       </c>
       <c r="V86">
-        <v>3.76282855318909</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>3.7628285531890899</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>941</v>
       </c>
@@ -6430,13 +6633,13 @@
         <v>11.1</v>
       </c>
       <c r="E87">
-        <v>38.02521008</v>
+        <v>38.025210080000001</v>
       </c>
       <c r="F87">
-        <v>13.58950328</v>
+        <v>13.589503280000001</v>
       </c>
       <c r="G87">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H87">
         <v>379.0905449</v>
@@ -6448,50 +6651,48 @@
         <v>32.42718447</v>
       </c>
       <c r="K87">
-        <v>9.465791940000001</v>
+        <v>9.4657919400000008</v>
       </c>
       <c r="L87">
         <v>5274</v>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Parkwood Hills - Stewart Farm</t>
-        </is>
+      <c r="M87" t="s">
+        <v>107</v>
       </c>
       <c r="N87">
         <v>102.3670135834782</v>
       </c>
       <c r="O87">
-        <v>1.045322978786657</v>
+        <v>1.0453229787866569</v>
       </c>
       <c r="P87">
-        <v>3.68639434678386</v>
+        <v>3.6863943467838598</v>
       </c>
       <c r="Q87">
-        <v>5.289999999999999</v>
+        <v>5.2899999999999991</v>
       </c>
       <c r="R87">
         <v>2.578742952590602</v>
       </c>
       <c r="S87">
-        <v>3.267967510548414</v>
+        <v>3.2679675105484138</v>
       </c>
       <c r="T87">
         <v>5.694487199915371</v>
       </c>
       <c r="U87">
-        <v>0.9761569543573128</v>
+        <v>0.97615695435731276</v>
       </c>
       <c r="V87">
         <v>3.722140125457416</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>942</v>
       </c>
       <c r="B88">
-        <v>2909.382119</v>
+        <v>2909.3821189999999</v>
       </c>
       <c r="C88">
         <v>92558</v>
@@ -6500,7 +6701,7 @@
         <v>6.4</v>
       </c>
       <c r="E88">
-        <v>22.03891709</v>
+        <v>22.038917090000002</v>
       </c>
       <c r="F88">
         <v>2.9296875</v>
@@ -6509,30 +6710,28 @@
         <v>3</v>
       </c>
       <c r="H88">
-        <v>535.3970394</v>
+        <v>535.39703940000004</v>
       </c>
       <c r="I88">
         <v>3.69793694</v>
       </c>
       <c r="J88">
-        <v>44.06383807</v>
+        <v>44.063838070000003</v>
       </c>
       <c r="K88">
-        <v>6.989364011</v>
+        <v>6.9893640110000002</v>
       </c>
       <c r="L88">
         <v>5286</v>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Portobello South</t>
-        </is>
+      <c r="M88" t="s">
+        <v>108</v>
       </c>
       <c r="N88">
-        <v>53.93868851761229</v>
+        <v>53.938688517612292</v>
       </c>
       <c r="O88">
-        <v>0.8061799739838872</v>
+        <v>0.80617997398388719</v>
       </c>
       <c r="P88">
         <v>1.711632992203644</v>
@@ -6541,27 +6740,27 @@
         <v>9</v>
       </c>
       <c r="R88">
-        <v>2.728675965327197</v>
+        <v>2.7286759653271968</v>
       </c>
       <c r="S88">
-        <v>1.923002064481471</v>
+        <v>1.9230020644814709</v>
       </c>
       <c r="T88">
-        <v>6.638059812174037</v>
+        <v>6.6380598121740366</v>
       </c>
       <c r="U88">
-        <v>0.8444376594253075</v>
+        <v>0.84443765942530746</v>
       </c>
       <c r="V88">
         <v>3.723127158795692</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>943</v>
       </c>
       <c r="B89">
-        <v>2779.06363</v>
+        <v>2779.0636300000001</v>
       </c>
       <c r="C89">
         <v>85416</v>
@@ -6573,65 +6772,63 @@
         <v>23.49048801</v>
       </c>
       <c r="F89">
-        <v>0.857843137</v>
+        <v>0.85784313700000003</v>
       </c>
       <c r="G89">
         <v>2.6</v>
       </c>
       <c r="H89">
-        <v>413.2267815</v>
+        <v>413.22678150000002</v>
       </c>
       <c r="I89">
-        <v>5.135730007</v>
+        <v>5.1357300070000003</v>
       </c>
       <c r="J89">
-        <v>31.32795304</v>
+        <v>31.327953040000001</v>
       </c>
       <c r="K89">
-        <v>18.66830065</v>
+        <v>18.668300649999999</v>
       </c>
       <c r="L89">
         <v>2801</v>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Queenswood Heights</t>
-        </is>
+      <c r="M89" t="s">
+        <v>109</v>
       </c>
       <c r="N89">
-        <v>52.7168249233582</v>
+        <v>52.716824923358203</v>
       </c>
       <c r="O89">
-        <v>0.7634279935629372</v>
+        <v>0.76342799356293722</v>
       </c>
       <c r="P89">
-        <v>0.926198216906079</v>
+        <v>0.92619821690607895</v>
       </c>
       <c r="Q89">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R89">
-        <v>2.616188460671278</v>
+        <v>2.6161884606712782</v>
       </c>
       <c r="S89">
-        <v>2.266214907505464</v>
+        <v>2.2662149075054638</v>
       </c>
       <c r="T89">
-        <v>5.597137932908211</v>
+        <v>5.5971379329082112</v>
       </c>
       <c r="U89">
         <v>1.271104786512699</v>
       </c>
       <c r="V89">
-        <v>3.447313108823568</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>3.4473131088235678</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>944</v>
       </c>
       <c r="B90">
-        <v>44.63051775</v>
+        <v>44.630517750000003</v>
       </c>
       <c r="C90">
         <v>90595</v>
@@ -6640,22 +6837,22 @@
         <v>5.2</v>
       </c>
       <c r="E90">
-        <v>5.832147937</v>
+        <v>5.8321479370000002</v>
       </c>
       <c r="F90">
-        <v>0.331785003</v>
+        <v>0.33178500300000002</v>
       </c>
       <c r="G90">
         <v>2.7</v>
       </c>
       <c r="H90">
-        <v>18.23128515</v>
+        <v>18.231285150000001</v>
       </c>
       <c r="I90">
-        <v>4.834605598</v>
+        <v>4.8346055979999996</v>
       </c>
       <c r="J90">
-        <v>33.84223919</v>
+        <v>33.842239190000001</v>
       </c>
       <c r="K90">
         <v>17.91639018</v>
@@ -6663,45 +6860,43 @@
       <c r="L90">
         <v>3349</v>
       </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
+      <c r="M90" t="s">
+        <v>110</v>
       </c>
       <c r="N90">
-        <v>6.680607588385954</v>
+        <v>6.6806075883859544</v>
       </c>
       <c r="O90">
-        <v>0.7160033436347992</v>
+        <v>0.71600334363479923</v>
       </c>
       <c r="P90">
-        <v>0.5760078150511502</v>
+        <v>0.57600781505115017</v>
       </c>
       <c r="Q90">
-        <v>7.290000000000001</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="R90">
-        <v>1.260817283788335</v>
+        <v>1.2608172837883349</v>
       </c>
       <c r="S90">
-        <v>2.198773657746517</v>
+        <v>2.1987736577465169</v>
       </c>
       <c r="T90">
-        <v>5.81740828806093</v>
+        <v>5.8174082880609301</v>
       </c>
       <c r="U90">
-        <v>1.253250511864623</v>
+        <v>1.2532505118646231</v>
       </c>
       <c r="V90">
         <v>3.524915147539867</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>945</v>
       </c>
       <c r="B91">
-        <v>3019.37798</v>
+        <v>3019.3779800000002</v>
       </c>
       <c r="C91">
         <v>96090</v>
@@ -6710,68 +6905,66 @@
         <v>5.2</v>
       </c>
       <c r="E91">
-        <v>18.07387863</v>
+        <v>18.073878629999999</v>
       </c>
       <c r="F91">
-        <v>2.418797512</v>
+        <v>2.4187975119999998</v>
       </c>
       <c r="G91">
         <v>3.1</v>
       </c>
       <c r="H91">
-        <v>834.0327428000001</v>
+        <v>834.03274280000005</v>
       </c>
       <c r="I91">
         <v>4.29022082</v>
       </c>
       <c r="J91">
-        <v>49.96845426</v>
+        <v>49.968454260000001</v>
       </c>
       <c r="K91">
-        <v>7.636489288</v>
+        <v>7.6364892879999999</v>
       </c>
       <c r="L91">
         <v>3201</v>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Rideau Crest - Davidson Heights</t>
-        </is>
+      <c r="M91" t="s">
+        <v>111</v>
       </c>
       <c r="N91">
-        <v>54.94886695829133</v>
+        <v>54.948866958291333</v>
       </c>
       <c r="O91">
-        <v>0.7160033436347992</v>
+        <v>0.71600334363479923</v>
       </c>
       <c r="P91">
         <v>1.555248376305213</v>
       </c>
       <c r="Q91">
-        <v>9.610000000000001</v>
+        <v>9.6100000000000012</v>
       </c>
       <c r="R91">
-        <v>2.921183100683579</v>
+        <v>2.9211831006835789</v>
       </c>
       <c r="S91">
         <v>2.071284823485172</v>
       </c>
       <c r="T91">
-        <v>7.068836839254391</v>
+        <v>7.0688368392543914</v>
       </c>
       <c r="U91">
-        <v>0.8828937468917161</v>
+        <v>0.88289374689171607</v>
       </c>
       <c r="V91">
-        <v>3.505285674144132</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>3.5052856741441318</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>946</v>
       </c>
       <c r="B92">
-        <v>573.0829285</v>
+        <v>573.08292849999998</v>
       </c>
       <c r="C92">
         <v>100352</v>
@@ -6789,30 +6982,28 @@
         <v>2.9</v>
       </c>
       <c r="H92">
-        <v>51.05424949</v>
+        <v>51.054249489999997</v>
       </c>
       <c r="I92">
-        <v>2.860775588</v>
+        <v>2.8607755880000001</v>
       </c>
       <c r="J92">
-        <v>53.4647171</v>
+        <v>53.464717100000001</v>
       </c>
       <c r="K92">
-        <v>8.487874465000001</v>
+        <v>8.4878744650000009</v>
       </c>
       <c r="L92">
         <v>3558</v>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Riverside South - Leitrim</t>
-        </is>
+      <c r="M92" t="s">
+        <v>112</v>
       </c>
       <c r="N92">
-        <v>23.9391505383963</v>
+        <v>23.939150538396301</v>
       </c>
       <c r="O92">
-        <v>0.7160033436347992</v>
+        <v>0.71600334363479923</v>
       </c>
       <c r="P92">
         <v>1.668152506817048</v>
@@ -6821,27 +7012,27 @@
         <v>8.41</v>
       </c>
       <c r="R92">
-        <v>1.70803189633967</v>
+        <v>1.7080318963396699</v>
       </c>
       <c r="S92">
-        <v>1.691382744384014</v>
+        <v>1.6913827443840139</v>
       </c>
       <c r="T92">
-        <v>7.311957131985936</v>
+        <v>7.3119571319859364</v>
       </c>
       <c r="U92">
-        <v>0.9287989477593362</v>
+        <v>0.92879894775933625</v>
       </c>
       <c r="V92">
         <v>3.551205943747906</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>947</v>
       </c>
       <c r="B93">
-        <v>3353.06161</v>
+        <v>3353.0616100000002</v>
       </c>
       <c r="C93">
         <v>40117</v>
@@ -6850,16 +7041,16 @@
         <v>12.1</v>
       </c>
       <c r="E93">
-        <v>46.79802956</v>
+        <v>46.798029560000003</v>
       </c>
       <c r="F93">
-        <v>6.440957886</v>
+        <v>6.4409578859999996</v>
       </c>
       <c r="G93">
         <v>1.9</v>
       </c>
       <c r="H93">
-        <v>6635.794762</v>
+        <v>6635.7947620000004</v>
       </c>
       <c r="I93">
         <v>4.375</v>
@@ -6868,50 +7059,48 @@
         <v>59.53125</v>
       </c>
       <c r="K93">
-        <v>9.661436828999999</v>
+        <v>9.6614368289999994</v>
       </c>
       <c r="L93">
         <v>4815</v>
       </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Riverview</t>
-        </is>
+      <c r="M93" t="s">
+        <v>113</v>
       </c>
       <c r="N93">
-        <v>57.90562675595525</v>
+        <v>57.905626755955247</v>
       </c>
       <c r="O93">
-        <v>1.08278537031645</v>
+        <v>1.0827853703164501</v>
       </c>
       <c r="P93">
-        <v>2.537904231053646</v>
+        <v>2.5379042310536462</v>
       </c>
       <c r="Q93">
         <v>3.61</v>
       </c>
       <c r="R93">
-        <v>3.821892945298485</v>
+        <v>3.8218929452984849</v>
       </c>
       <c r="S93">
-        <v>2.091650066335189</v>
+        <v>2.0916500663351889</v>
       </c>
       <c r="T93">
-        <v>7.715649681005482</v>
+        <v>7.7156496810054822</v>
       </c>
       <c r="U93">
         <v>0.9850417186001027</v>
       </c>
       <c r="V93">
-        <v>3.682596291460553</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>3.6825962914605528</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>948</v>
       </c>
       <c r="B94">
-        <v>889.9863986</v>
+        <v>889.98639860000003</v>
       </c>
       <c r="C94">
         <v>189059</v>
@@ -6920,7 +7109,7 @@
         <v>5.7</v>
       </c>
       <c r="E94">
-        <v>9.316770185999999</v>
+        <v>9.3167701859999994</v>
       </c>
       <c r="F94">
         <v>2.25</v>
@@ -6929,13 +7118,13 @@
         <v>2.9</v>
       </c>
       <c r="H94">
-        <v>214.4867221</v>
+        <v>214.48672210000001</v>
       </c>
       <c r="I94">
-        <v>1.092896175</v>
+        <v>1.0928961749999999</v>
       </c>
       <c r="J94">
-        <v>81.42076503</v>
+        <v>81.420765029999998</v>
       </c>
       <c r="K94">
         <v>22.5</v>
@@ -6943,16 +7132,14 @@
       <c r="L94">
         <v>3199</v>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Rockcliffe Park</t>
-        </is>
+      <c r="M94" t="s">
+        <v>114</v>
       </c>
       <c r="N94">
-        <v>29.83263981949971</v>
+        <v>29.832639819499711</v>
       </c>
       <c r="O94">
-        <v>0.7558748556724915</v>
+        <v>0.75587485567249146</v>
       </c>
       <c r="P94">
         <v>1.5</v>
@@ -6961,22 +7148,22 @@
         <v>8.41</v>
       </c>
       <c r="R94">
-        <v>2.331400412151572</v>
+        <v>2.3314004121515719</v>
       </c>
       <c r="S94">
-        <v>1.045416747043972</v>
+        <v>1.0454167470439719</v>
       </c>
       <c r="T94">
-        <v>9.023345556388717</v>
+        <v>9.0233455563887173</v>
       </c>
       <c r="U94">
         <v>1.352182518111362</v>
       </c>
       <c r="V94">
-        <v>3.505014240084107</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>3.5050142400841069</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>949</v>
       </c>
@@ -6993,19 +7180,19 @@
         <v>29.47189097</v>
       </c>
       <c r="F95">
-        <v>3.702090592</v>
+        <v>3.7020905919999998</v>
       </c>
       <c r="G95">
         <v>1.8</v>
       </c>
       <c r="H95">
-        <v>9642.388771</v>
+        <v>9642.3887709999999</v>
       </c>
       <c r="I95">
-        <v>5.466778806</v>
+        <v>5.4667788059999998</v>
       </c>
       <c r="J95">
-        <v>66.1059714</v>
+        <v>66.105971400000001</v>
       </c>
       <c r="K95">
         <v>11.19337979</v>
@@ -7013,19 +7200,17 @@
       <c r="L95">
         <v>6223</v>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Sandy Hill</t>
-        </is>
+      <c r="M95" t="s">
+        <v>115</v>
       </c>
       <c r="N95">
-        <v>72.77284290860156</v>
+        <v>72.772842908601561</v>
       </c>
       <c r="O95">
         <v>1.103803720955957</v>
       </c>
       <c r="P95">
-        <v>1.924081752940867</v>
+        <v>1.9240817529408669</v>
       </c>
       <c r="Q95">
         <v>3.24</v>
@@ -7037,21 +7222,21 @@
         <v>2.338114369743276</v>
       </c>
       <c r="T95">
-        <v>8.130557877538294</v>
+        <v>8.1305578775382941</v>
       </c>
       <c r="U95">
-        <v>1.048961239568858</v>
+        <v>1.0489612395688579</v>
       </c>
       <c r="V95">
-        <v>3.793999800984471</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>3.7939998009844711</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>950</v>
       </c>
       <c r="B96">
-        <v>2146.840628</v>
+        <v>2146.8406279999999</v>
       </c>
       <c r="C96">
         <v>75647</v>
@@ -7063,7 +7248,7 @@
         <v>17.69436997</v>
       </c>
       <c r="F96">
-        <v>2.774427021</v>
+        <v>2.7744270210000002</v>
       </c>
       <c r="G96">
         <v>2.5</v>
@@ -7075,24 +7260,22 @@
         <v>7.322654462</v>
       </c>
       <c r="J96">
-        <v>43.02059497</v>
+        <v>43.020594969999998</v>
       </c>
       <c r="K96">
-        <v>20.5066345</v>
+        <v>20.506634500000001</v>
       </c>
       <c r="L96">
         <v>4271</v>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Skyline - Fisher Heights</t>
-        </is>
+      <c r="M96" t="s">
+        <v>116</v>
       </c>
       <c r="N96">
-        <v>46.33401156817743</v>
+        <v>46.334011568177431</v>
       </c>
       <c r="O96">
-        <v>0.9344984512435677</v>
+        <v>0.93449845124356767</v>
       </c>
       <c r="P96">
         <v>1.665661136305941</v>
@@ -7101,22 +7284,22 @@
         <v>6.25</v>
       </c>
       <c r="R96">
-        <v>3.159256382836931</v>
+        <v>3.1592563828369311</v>
       </c>
       <c r="S96">
         <v>2.706040365922135</v>
       </c>
       <c r="T96">
-        <v>6.55900868805645</v>
+        <v>6.5590086880564504</v>
       </c>
       <c r="U96">
-        <v>1.311894390840774</v>
+        <v>1.3118943908407741</v>
       </c>
       <c r="V96">
-        <v>3.630529571426824</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>3.6305295714268242</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>951</v>
       </c>
@@ -7127,10 +7310,10 @@
         <v>101471</v>
       </c>
       <c r="D97">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E97">
-        <v>12.39220696</v>
+        <v>12.392206959999999</v>
       </c>
       <c r="F97">
         <v>1.449506212</v>
@@ -7139,59 +7322,57 @@
         <v>2.9</v>
       </c>
       <c r="H97">
-        <v>392.7848364</v>
+        <v>392.78483640000002</v>
       </c>
       <c r="I97">
-        <v>2.579132474</v>
+        <v>2.5791324740000001</v>
       </c>
       <c r="J97">
-        <v>46.014068</v>
+        <v>46.014068000000002</v>
       </c>
       <c r="K97">
-        <v>11.54642459</v>
+        <v>11.546424590000001</v>
       </c>
       <c r="L97">
         <v>3479</v>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Stittsville</t>
-        </is>
+      <c r="M97" t="s">
+        <v>117</v>
       </c>
       <c r="N97">
-        <v>32.34902782155903</v>
+        <v>32.349027821559027</v>
       </c>
       <c r="O97">
-        <v>0.6434526764861874</v>
+        <v>0.64345267648618742</v>
       </c>
       <c r="P97">
-        <v>1.203954406113454</v>
+        <v>1.2039544061134539</v>
       </c>
       <c r="Q97">
         <v>8.41</v>
       </c>
       <c r="R97">
-        <v>2.594154713343727</v>
+        <v>2.5941547133437268</v>
       </c>
       <c r="S97">
         <v>1.605967768667852</v>
       </c>
       <c r="T97">
-        <v>6.783367010563412</v>
+        <v>6.7833670105634116</v>
       </c>
       <c r="U97">
-        <v>1.062447523516299</v>
+        <v>1.0624475235162989</v>
       </c>
       <c r="V97">
-        <v>3.541454428747589</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>3.5414544287475889</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>952</v>
       </c>
       <c r="B98">
-        <v>1144.072323</v>
+        <v>1144.0723230000001</v>
       </c>
       <c r="C98">
         <v>98817</v>
@@ -7200,10 +7381,10 @@
         <v>5</v>
       </c>
       <c r="E98">
-        <v>15.65435191</v>
+        <v>15.654351910000001</v>
       </c>
       <c r="F98">
-        <v>3.580024067</v>
+        <v>3.5800240670000001</v>
       </c>
       <c r="G98">
         <v>3</v>
@@ -7212,27 +7393,25 @@
         <v>156.2601789</v>
       </c>
       <c r="I98">
-        <v>2.580645161</v>
+        <v>2.5806451610000001</v>
       </c>
       <c r="J98">
-        <v>54.08602151</v>
+        <v>54.086021510000002</v>
       </c>
       <c r="K98">
-        <v>7.791817088</v>
+        <v>7.7918170880000002</v>
       </c>
       <c r="L98">
         <v>4515</v>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Stonebridge - Half Moon Bay - Heart's Desire</t>
-        </is>
+      <c r="M98" t="s">
+        <v>118</v>
       </c>
       <c r="N98">
-        <v>33.82413817083889</v>
+        <v>33.824138170838893</v>
       </c>
       <c r="O98">
-        <v>0.6989700043360189</v>
+        <v>0.69897000433601886</v>
       </c>
       <c r="P98">
         <v>1.892095152734133</v>
@@ -7241,39 +7420,39 @@
         <v>9</v>
       </c>
       <c r="R98">
-        <v>2.193848317191261</v>
+        <v>2.1938483171912608</v>
       </c>
       <c r="S98">
-        <v>1.606438657714636</v>
+        <v>1.6064386577146359</v>
       </c>
       <c r="T98">
-        <v>7.354319921651491</v>
+        <v>7.3543199216514914</v>
       </c>
       <c r="U98">
-        <v>0.8916387489777637</v>
+        <v>0.89163874897776374</v>
       </c>
       <c r="V98">
         <v>3.654657754649524</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>953</v>
       </c>
       <c r="B99">
-        <v>6059.377914</v>
+        <v>6059.3779139999997</v>
       </c>
       <c r="C99">
         <v>46681</v>
       </c>
       <c r="D99">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E99">
-        <v>28.05907173</v>
+        <v>28.059071729999999</v>
       </c>
       <c r="F99">
-        <v>3.294573643</v>
+        <v>3.2945736430000001</v>
       </c>
       <c r="G99">
         <v>1.8</v>
@@ -7282,56 +7461,54 @@
         <v>1423.83638</v>
       </c>
       <c r="I99">
-        <v>15.03469545</v>
+        <v>15.034695449999999</v>
       </c>
       <c r="J99">
-        <v>34.84965305</v>
+        <v>34.849653050000001</v>
       </c>
       <c r="K99">
-        <v>16.13372093</v>
+        <v>16.133720929999999</v>
       </c>
       <c r="L99">
         <v>3698</v>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Vanier North</t>
-        </is>
+      <c r="M99" t="s">
+        <v>119</v>
       </c>
       <c r="N99">
-        <v>77.84200610210402</v>
+        <v>77.842006102104023</v>
       </c>
       <c r="O99">
         <v>1.008600171761918</v>
       </c>
       <c r="P99">
-        <v>1.815096042362497</v>
+        <v>1.8150960423624971</v>
       </c>
       <c r="Q99">
         <v>3.24</v>
       </c>
       <c r="R99">
-        <v>3.153460085265826</v>
+        <v>3.1534600852658259</v>
       </c>
       <c r="S99">
-        <v>3.877459922423441</v>
+        <v>3.8774599224234412</v>
       </c>
       <c r="T99">
-        <v>5.90335947152128</v>
+        <v>5.9033594715212798</v>
       </c>
       <c r="U99">
         <v>1.207734540544886</v>
       </c>
       <c r="V99">
-        <v>3.567966906823154</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>3.5679669068231541</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>954</v>
       </c>
       <c r="B100">
-        <v>4913.061979</v>
+        <v>4913.0619790000001</v>
       </c>
       <c r="C100">
         <v>38290</v>
@@ -7343,7 +7520,7 @@
         <v>32.09876543</v>
       </c>
       <c r="F100">
-        <v>5.729564553</v>
+        <v>5.7295645530000003</v>
       </c>
       <c r="G100">
         <v>1.8</v>
@@ -7352,10 +7529,10 @@
         <v>4227.937739</v>
       </c>
       <c r="I100">
-        <v>18.16976127</v>
+        <v>18.169761269999999</v>
       </c>
       <c r="J100">
-        <v>24.53580902</v>
+        <v>24.535809019999999</v>
       </c>
       <c r="K100">
         <v>19.49541284</v>
@@ -7363,31 +7540,29 @@
       <c r="L100">
         <v>5084</v>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Vanier South</t>
-        </is>
+      <c r="M100" t="s">
+        <v>120</v>
       </c>
       <c r="N100">
-        <v>70.0932377551501</v>
+        <v>70.093237755150099</v>
       </c>
       <c r="O100">
         <v>1.012837224705172</v>
       </c>
       <c r="P100">
-        <v>2.393650883692106</v>
+        <v>2.3936508836921062</v>
       </c>
       <c r="Q100">
         <v>3.24</v>
       </c>
       <c r="R100">
-        <v>3.626128583221994</v>
+        <v>3.6261285832219938</v>
       </c>
       <c r="S100">
-        <v>4.262600294421235</v>
+        <v>4.2626002944212349</v>
       </c>
       <c r="T100">
-        <v>4.953363404798804</v>
+        <v>4.9533634047988038</v>
       </c>
       <c r="U100">
         <v>1.289932436355782</v>
@@ -7396,12 +7571,12 @@
         <v>3.706205541881971</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>955</v>
       </c>
       <c r="B101">
-        <v>32.94810187</v>
+        <v>32.948101870000002</v>
       </c>
       <c r="C101">
         <v>86507</v>
@@ -7410,54 +7585,52 @@
         <v>2.6</v>
       </c>
       <c r="E101">
-        <v>4.225352113</v>
+        <v>4.2253521129999996</v>
       </c>
       <c r="F101">
-        <v>0.589390963</v>
+        <v>0.58939096300000005</v>
       </c>
       <c r="G101">
         <v>2.6</v>
       </c>
       <c r="H101">
-        <v>7.575469092</v>
+        <v>7.5754690919999996</v>
       </c>
       <c r="I101">
-        <v>9.900990098999999</v>
+        <v>9.9009900989999995</v>
       </c>
       <c r="J101">
-        <v>19.14191419</v>
+        <v>19.141914190000001</v>
       </c>
       <c r="K101">
-        <v>14.76377953</v>
+        <v>14.763779530000001</v>
       </c>
       <c r="L101">
         <v>3903</v>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>Vars</t>
-        </is>
+      <c r="M101" t="s">
+        <v>121</v>
       </c>
       <c r="N101">
-        <v>5.740043716732478</v>
+        <v>5.7400437167324778</v>
       </c>
       <c r="O101">
-        <v>0.414973347970818</v>
+        <v>0.41497334797081797</v>
       </c>
       <c r="P101">
-        <v>0.7677180231048376</v>
+        <v>0.76771802310483761</v>
       </c>
       <c r="Q101">
-        <v>6.760000000000001</v>
+        <v>6.7600000000000007</v>
       </c>
       <c r="R101">
-        <v>0.8794095306079298</v>
+        <v>0.87940953060792981</v>
       </c>
       <c r="S101">
-        <v>3.14658387763619</v>
+        <v>3.1465838776361901</v>
       </c>
       <c r="T101">
-        <v>4.375147333519181</v>
+        <v>4.3751473335191813</v>
       </c>
       <c r="U101">
         <v>1.169197551179584</v>
@@ -7466,30 +7639,30 @@
         <v>3.591398551281249</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>957</v>
       </c>
       <c r="B102">
-        <v>5298.494736</v>
+        <v>5298.4947359999996</v>
       </c>
       <c r="C102">
         <v>43328</v>
       </c>
       <c r="D102">
-        <v>8.800000000000001</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="E102">
-        <v>25.22889115</v>
+        <v>25.228891149999999</v>
       </c>
       <c r="F102">
-        <v>4.175475687</v>
+        <v>4.1754756869999996</v>
       </c>
       <c r="G102">
         <v>1.8</v>
       </c>
       <c r="H102">
-        <v>7159.128935</v>
+        <v>7159.1289349999997</v>
       </c>
       <c r="I102">
         <v>11.2833764</v>
@@ -7498,21 +7671,19 @@
         <v>50.21533161</v>
       </c>
       <c r="K102">
-        <v>14.9577167</v>
+        <v>14.957716700000001</v>
       </c>
       <c r="L102">
         <v>3973</v>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>West Centretown</t>
-        </is>
+      <c r="M102" t="s">
+        <v>122</v>
       </c>
       <c r="N102">
-        <v>72.79075996306125</v>
+        <v>72.790759963061248</v>
       </c>
       <c r="O102">
-        <v>0.9444826721501687</v>
+        <v>0.94448267215016868</v>
       </c>
       <c r="P102">
         <v>2.043398073552972</v>
@@ -7521,68 +7692,66 @@
         <v>3.24</v>
       </c>
       <c r="R102">
-        <v>3.854860184076555</v>
+        <v>3.8548601840765548</v>
       </c>
       <c r="S102">
-        <v>3.359073741375738</v>
+        <v>3.3590737413757381</v>
       </c>
       <c r="T102">
-        <v>7.086277697776175</v>
+        <v>7.0862776977761754</v>
       </c>
       <c r="U102">
-        <v>1.17486530340327</v>
+        <v>1.1748653034032699</v>
       </c>
       <c r="V102">
-        <v>3.599118565055363</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>3.5991185650553632</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>958</v>
       </c>
       <c r="B103">
-        <v>3611.215419</v>
+        <v>3611.2154190000001</v>
       </c>
       <c r="C103">
         <v>67336</v>
       </c>
       <c r="D103">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E103">
         <v>25.55350554</v>
       </c>
       <c r="F103">
-        <v>1.791958042</v>
+        <v>1.7919580420000001</v>
       </c>
       <c r="G103">
         <v>2</v>
       </c>
       <c r="H103">
-        <v>2071.398215</v>
+        <v>2071.3982150000002</v>
       </c>
       <c r="I103">
         <v>3.948367502</v>
       </c>
       <c r="J103">
-        <v>62.18678815</v>
+        <v>62.186788149999998</v>
       </c>
       <c r="K103">
-        <v>19.97377622</v>
+        <v>19.973776220000001</v>
       </c>
       <c r="L103">
         <v>2655</v>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>Westboro</t>
-        </is>
+      <c r="M103" t="s">
+        <v>123</v>
       </c>
       <c r="N103">
-        <v>60.09338914556243</v>
+        <v>60.093389145562433</v>
       </c>
       <c r="O103">
-        <v>0.6901960800285137</v>
+        <v>0.69019608002851374</v>
       </c>
       <c r="P103">
         <v>1.338640370674663</v>
@@ -7591,19 +7760,19 @@
         <v>4</v>
       </c>
       <c r="R103">
-        <v>3.316263597663328</v>
+        <v>3.3162635976633279</v>
       </c>
       <c r="S103">
-        <v>1.987049949548325</v>
+        <v>1.9870499495483249</v>
       </c>
       <c r="T103">
-        <v>7.885860013340333</v>
+        <v>7.8858600133403334</v>
       </c>
       <c r="U103">
-        <v>1.300460179866756</v>
+        <v>1.3004601798667561</v>
       </c>
       <c r="V103">
-        <v>3.424064525417488</v>
+        <v>3.4240645254174882</v>
       </c>
     </row>
   </sheetData>
